--- a/Data_Structures_and_Algorithms.xlsx
+++ b/Data_Structures_and_Algorithms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nvjsi\Desktop\My Projects\pro-data-structures-and-algorithms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE74880-7E75-4C6C-AD76-194C3076E565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0A86C4-ED72-442D-BFBE-75A4D7B2EE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{463DEBCD-443E-4114-A884-3BF4F43F1855}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
   <si>
     <t>Data Structures and Algorithms</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>Concurrency</t>
+  </si>
+  <si>
+    <t>binary search</t>
   </si>
 </sst>
 </file>
@@ -390,6 +393,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -408,16 +432,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -429,25 +450,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -797,22 +800,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="22"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="9"/>
     </row>
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="G3" s="23"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="25"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="12"/>
     </row>
     <row r="5" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2"/>
@@ -833,35 +836,35 @@
     </row>
     <row r="6" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="1"/>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="15"/>
       <c r="F6" s="5"/>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="11"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="18"/>
       <c r="M6" s="1"/>
-      <c r="N6" s="6" t="s">
+      <c r="N6" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="O6" s="7"/>
-      <c r="P6" s="8"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="15"/>
       <c r="Q6" s="5"/>
-      <c r="R6" s="9" t="s">
+      <c r="R6" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="S6" s="10"/>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10"/>
-      <c r="V6" s="10"/>
-      <c r="W6" s="11"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="18"/>
     </row>
     <row r="7" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1"/>
@@ -869,25 +872,25 @@
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
       <c r="M7" s="1"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="12"/>
-      <c r="V7" s="12"/>
-      <c r="W7" s="12"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
     </row>
     <row r="8" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1"/>
@@ -895,908 +898,987 @@
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
       <c r="M8" s="1"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="12"/>
-      <c r="W8" s="12"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="6"/>
+      <c r="U8" s="6"/>
+      <c r="V8" s="6"/>
+      <c r="W8" s="6"/>
     </row>
     <row r="9" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
-      <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="12"/>
-      <c r="W9" s="12"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="6"/>
+      <c r="U9" s="6"/>
+      <c r="V9" s="6"/>
+      <c r="W9" s="6"/>
     </row>
     <row r="11" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="8"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="15"/>
       <c r="F11" s="5"/>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="11"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="18"/>
     </row>
     <row r="12" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
     </row>
     <row r="13" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
     </row>
     <row r="14" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
     </row>
     <row r="16" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="19"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="21"/>
       <c r="F16" s="4"/>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="18"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="24"/>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
     </row>
     <row r="21" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="14"/>
-      <c r="E21" s="15"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="25"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="16" t="s">
+      <c r="G21" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="18"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="23"/>
+      <c r="L21" s="24"/>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="7"/>
-      <c r="E26" s="8"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="15"/>
       <c r="F26" s="5"/>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="11"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="18"/>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
-      <c r="G27" s="12" t="s">
+      <c r="G27" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
     </row>
     <row r="28" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
     </row>
     <row r="29" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="7"/>
-      <c r="E31" s="8"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="15"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="9" t="s">
+      <c r="G31" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="11"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="18"/>
     </row>
     <row r="32" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
     </row>
     <row r="36" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D36" s="7"/>
-      <c r="E36" s="8"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="15"/>
       <c r="F36" s="5"/>
-      <c r="G36" s="9" t="s">
+      <c r="G36" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="11"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="18"/>
     </row>
     <row r="37" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="12"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="12"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
     </row>
     <row r="38" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="12"/>
-      <c r="J38" s="12"/>
-      <c r="K38" s="12"/>
-      <c r="L38" s="12"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
     </row>
     <row r="39" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="12"/>
-      <c r="K39" s="12"/>
-      <c r="L39" s="12"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
     </row>
     <row r="41" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="7"/>
-      <c r="E41" s="8"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="15"/>
       <c r="F41" s="5"/>
-      <c r="G41" s="9" t="s">
+      <c r="G41" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="11"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="18"/>
     </row>
     <row r="42" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="12"/>
-      <c r="J42" s="12"/>
-      <c r="K42" s="12"/>
-      <c r="L42" s="12"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
     </row>
     <row r="43" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="12"/>
-      <c r="J43" s="12"/>
-      <c r="K43" s="12"/>
-      <c r="L43" s="12"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
     </row>
     <row r="44" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
-      <c r="I44" s="12"/>
-      <c r="J44" s="12"/>
-      <c r="K44" s="12"/>
-      <c r="L44" s="12"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
     </row>
     <row r="46" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="7"/>
-      <c r="E46" s="8"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="15"/>
       <c r="F46" s="5"/>
-      <c r="G46" s="9" t="s">
+      <c r="G46" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="11"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="18"/>
     </row>
     <row r="47" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
-      <c r="G47" s="12"/>
-      <c r="H47" s="12"/>
-      <c r="I47" s="12"/>
-      <c r="J47" s="12"/>
-      <c r="K47" s="12"/>
-      <c r="L47" s="12"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="6"/>
     </row>
     <row r="48" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="12"/>
-      <c r="I48" s="12"/>
-      <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
-      <c r="L48" s="12"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
     </row>
     <row r="49" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G49" s="12"/>
-      <c r="H49" s="12"/>
-      <c r="I49" s="12"/>
-      <c r="J49" s="12"/>
-      <c r="K49" s="12"/>
-      <c r="L49" s="12"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="6"/>
     </row>
     <row r="51" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="7"/>
-      <c r="E51" s="8"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="15"/>
       <c r="F51" s="5"/>
-      <c r="G51" s="9" t="s">
+      <c r="G51" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="11"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="17"/>
+      <c r="J51" s="17"/>
+      <c r="K51" s="17"/>
+      <c r="L51" s="18"/>
     </row>
     <row r="52" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
-      <c r="I52" s="12"/>
-      <c r="J52" s="12"/>
-      <c r="K52" s="12"/>
-      <c r="L52" s="12"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
     </row>
     <row r="53" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="12"/>
-      <c r="I53" s="12"/>
-      <c r="J53" s="12"/>
-      <c r="K53" s="12"/>
-      <c r="L53" s="12"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="6"/>
     </row>
     <row r="54" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
-      <c r="K54" s="12"/>
-      <c r="L54" s="12"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
     </row>
     <row r="56" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D56" s="7"/>
-      <c r="E56" s="8"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="15"/>
       <c r="F56" s="5"/>
-      <c r="G56" s="9" t="s">
+      <c r="G56" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H56" s="10"/>
-      <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
-      <c r="K56" s="10"/>
-      <c r="L56" s="11"/>
+      <c r="H56" s="17"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="17"/>
+      <c r="K56" s="17"/>
+      <c r="L56" s="18"/>
     </row>
     <row r="57" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
-      <c r="K57" s="12"/>
-      <c r="L57" s="12"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="6"/>
     </row>
     <row r="58" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
-      <c r="K58" s="12"/>
-      <c r="L58" s="12"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6"/>
+      <c r="L58" s="6"/>
     </row>
     <row r="59" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G59" s="12"/>
-      <c r="H59" s="12"/>
-      <c r="I59" s="12"/>
-      <c r="J59" s="12"/>
-      <c r="K59" s="12"/>
-      <c r="L59" s="12"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
     </row>
     <row r="61" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D61" s="7"/>
-      <c r="E61" s="8"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="15"/>
       <c r="F61" s="5"/>
-      <c r="G61" s="9" t="s">
+      <c r="G61" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H61" s="10"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
-      <c r="K61" s="10"/>
-      <c r="L61" s="11"/>
+      <c r="H61" s="17"/>
+      <c r="I61" s="17"/>
+      <c r="J61" s="17"/>
+      <c r="K61" s="17"/>
+      <c r="L61" s="18"/>
     </row>
     <row r="62" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
-      <c r="G62" s="12"/>
-      <c r="H62" s="12"/>
-      <c r="I62" s="12"/>
-      <c r="J62" s="12"/>
-      <c r="K62" s="12"/>
-      <c r="L62" s="12"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
     </row>
     <row r="63" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
-      <c r="G63" s="12"/>
-      <c r="H63" s="12"/>
-      <c r="I63" s="12"/>
-      <c r="J63" s="12"/>
-      <c r="K63" s="12"/>
-      <c r="L63" s="12"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
     </row>
     <row r="64" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G64" s="12"/>
-      <c r="H64" s="12"/>
-      <c r="I64" s="12"/>
-      <c r="J64" s="12"/>
-      <c r="K64" s="12"/>
-      <c r="L64" s="12"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6"/>
+      <c r="L64" s="6"/>
     </row>
     <row r="66" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D66" s="7"/>
-      <c r="E66" s="8"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="15"/>
       <c r="F66" s="5"/>
-      <c r="G66" s="9" t="s">
+      <c r="G66" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H66" s="10"/>
-      <c r="I66" s="10"/>
-      <c r="J66" s="10"/>
-      <c r="K66" s="10"/>
-      <c r="L66" s="11"/>
+      <c r="H66" s="17"/>
+      <c r="I66" s="17"/>
+      <c r="J66" s="17"/>
+      <c r="K66" s="17"/>
+      <c r="L66" s="18"/>
     </row>
     <row r="67" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
-      <c r="G67" s="12"/>
-      <c r="H67" s="12"/>
-      <c r="I67" s="12"/>
-      <c r="J67" s="12"/>
-      <c r="K67" s="12"/>
-      <c r="L67" s="12"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="6"/>
     </row>
     <row r="68" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
-      <c r="G68" s="12"/>
-      <c r="H68" s="12"/>
-      <c r="I68" s="12"/>
-      <c r="J68" s="12"/>
-      <c r="K68" s="12"/>
-      <c r="L68" s="12"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="6"/>
+      <c r="J68" s="6"/>
+      <c r="K68" s="6"/>
+      <c r="L68" s="6"/>
     </row>
     <row r="69" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G69" s="12"/>
-      <c r="H69" s="12"/>
-      <c r="I69" s="12"/>
-      <c r="J69" s="12"/>
-      <c r="K69" s="12"/>
-      <c r="L69" s="12"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
+      <c r="K69" s="6"/>
+      <c r="L69" s="6"/>
     </row>
     <row r="71" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C71" s="6" t="s">
+      <c r="C71" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D71" s="7"/>
-      <c r="E71" s="8"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="15"/>
       <c r="F71" s="5"/>
-      <c r="G71" s="9" t="s">
+      <c r="G71" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H71" s="10"/>
-      <c r="I71" s="10"/>
-      <c r="J71" s="10"/>
-      <c r="K71" s="10"/>
-      <c r="L71" s="11"/>
+      <c r="H71" s="17"/>
+      <c r="I71" s="17"/>
+      <c r="J71" s="17"/>
+      <c r="K71" s="17"/>
+      <c r="L71" s="18"/>
     </row>
     <row r="72" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
-      <c r="G72" s="12"/>
-      <c r="H72" s="12"/>
-      <c r="I72" s="12"/>
-      <c r="J72" s="12"/>
-      <c r="K72" s="12"/>
-      <c r="L72" s="12"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6"/>
+      <c r="J72" s="6"/>
+      <c r="K72" s="6"/>
+      <c r="L72" s="6"/>
     </row>
     <row r="73" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
-      <c r="G73" s="12"/>
-      <c r="H73" s="12"/>
-      <c r="I73" s="12"/>
-      <c r="J73" s="12"/>
-      <c r="K73" s="12"/>
-      <c r="L73" s="12"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="6"/>
+      <c r="J73" s="6"/>
+      <c r="K73" s="6"/>
+      <c r="L73" s="6"/>
     </row>
     <row r="74" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G74" s="12"/>
-      <c r="H74" s="12"/>
-      <c r="I74" s="12"/>
-      <c r="J74" s="12"/>
-      <c r="K74" s="12"/>
-      <c r="L74" s="12"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="6"/>
     </row>
     <row r="76" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C76" s="6" t="s">
+      <c r="C76" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D76" s="7"/>
-      <c r="E76" s="8"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="15"/>
       <c r="F76" s="5"/>
-      <c r="G76" s="9" t="s">
+      <c r="G76" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H76" s="10"/>
-      <c r="I76" s="10"/>
-      <c r="J76" s="10"/>
-      <c r="K76" s="10"/>
-      <c r="L76" s="11"/>
+      <c r="H76" s="17"/>
+      <c r="I76" s="17"/>
+      <c r="J76" s="17"/>
+      <c r="K76" s="17"/>
+      <c r="L76" s="18"/>
     </row>
     <row r="77" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
-      <c r="G77" s="12"/>
-      <c r="H77" s="12"/>
-      <c r="I77" s="12"/>
-      <c r="J77" s="12"/>
-      <c r="K77" s="12"/>
-      <c r="L77" s="12"/>
+      <c r="G77" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H77" s="6"/>
+      <c r="I77" s="6"/>
+      <c r="J77" s="6"/>
+      <c r="K77" s="6"/>
+      <c r="L77" s="6"/>
     </row>
     <row r="78" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
-      <c r="G78" s="12"/>
-      <c r="H78" s="12"/>
-      <c r="I78" s="12"/>
-      <c r="J78" s="12"/>
-      <c r="K78" s="12"/>
-      <c r="L78" s="12"/>
+      <c r="G78" s="6"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="6"/>
+      <c r="J78" s="6"/>
+      <c r="K78" s="6"/>
+      <c r="L78" s="6"/>
     </row>
     <row r="79" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G79" s="12"/>
-      <c r="H79" s="12"/>
-      <c r="I79" s="12"/>
-      <c r="J79" s="12"/>
-      <c r="K79" s="12"/>
-      <c r="L79" s="12"/>
+      <c r="G79" s="6"/>
+      <c r="H79" s="6"/>
+      <c r="I79" s="6"/>
+      <c r="J79" s="6"/>
+      <c r="K79" s="6"/>
+      <c r="L79" s="6"/>
     </row>
     <row r="81" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C81" s="6" t="s">
+      <c r="C81" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D81" s="7"/>
-      <c r="E81" s="8"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="15"/>
       <c r="F81" s="5"/>
-      <c r="G81" s="9" t="s">
+      <c r="G81" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H81" s="10"/>
-      <c r="I81" s="10"/>
-      <c r="J81" s="10"/>
-      <c r="K81" s="10"/>
-      <c r="L81" s="11"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="17"/>
+      <c r="K81" s="17"/>
+      <c r="L81" s="18"/>
     </row>
     <row r="82" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
-      <c r="G82" s="12"/>
-      <c r="H82" s="12"/>
-      <c r="I82" s="12"/>
-      <c r="J82" s="12"/>
-      <c r="K82" s="12"/>
-      <c r="L82" s="12"/>
+      <c r="G82" s="6"/>
+      <c r="H82" s="6"/>
+      <c r="I82" s="6"/>
+      <c r="J82" s="6"/>
+      <c r="K82" s="6"/>
+      <c r="L82" s="6"/>
     </row>
     <row r="83" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
-      <c r="G83" s="12"/>
-      <c r="H83" s="12"/>
-      <c r="I83" s="12"/>
-      <c r="J83" s="12"/>
-      <c r="K83" s="12"/>
-      <c r="L83" s="12"/>
+      <c r="G83" s="6"/>
+      <c r="H83" s="6"/>
+      <c r="I83" s="6"/>
+      <c r="J83" s="6"/>
+      <c r="K83" s="6"/>
+      <c r="L83" s="6"/>
     </row>
     <row r="84" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G84" s="12"/>
-      <c r="H84" s="12"/>
-      <c r="I84" s="12"/>
-      <c r="J84" s="12"/>
-      <c r="K84" s="12"/>
-      <c r="L84" s="12"/>
+      <c r="G84" s="6"/>
+      <c r="H84" s="6"/>
+      <c r="I84" s="6"/>
+      <c r="J84" s="6"/>
+      <c r="K84" s="6"/>
+      <c r="L84" s="6"/>
     </row>
     <row r="86" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C86" s="6" t="s">
+      <c r="C86" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D86" s="7"/>
-      <c r="E86" s="8"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="15"/>
       <c r="F86" s="5"/>
-      <c r="G86" s="9" t="s">
+      <c r="G86" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H86" s="10"/>
-      <c r="I86" s="10"/>
-      <c r="J86" s="10"/>
-      <c r="K86" s="10"/>
-      <c r="L86" s="11"/>
+      <c r="H86" s="17"/>
+      <c r="I86" s="17"/>
+      <c r="J86" s="17"/>
+      <c r="K86" s="17"/>
+      <c r="L86" s="18"/>
     </row>
     <row r="87" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
-      <c r="G87" s="12" t="s">
+      <c r="G87" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="H87" s="12"/>
-      <c r="I87" s="12"/>
-      <c r="J87" s="12"/>
-      <c r="K87" s="12"/>
-      <c r="L87" s="12"/>
+      <c r="H87" s="6"/>
+      <c r="I87" s="6"/>
+      <c r="J87" s="6"/>
+      <c r="K87" s="6"/>
+      <c r="L87" s="6"/>
     </row>
     <row r="88" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
-      <c r="G88" s="12"/>
-      <c r="H88" s="12"/>
-      <c r="I88" s="12"/>
-      <c r="J88" s="12"/>
-      <c r="K88" s="12"/>
-      <c r="L88" s="12"/>
+      <c r="G88" s="6"/>
+      <c r="H88" s="6"/>
+      <c r="I88" s="6"/>
+      <c r="J88" s="6"/>
+      <c r="K88" s="6"/>
+      <c r="L88" s="6"/>
     </row>
     <row r="89" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G89" s="12"/>
-      <c r="H89" s="12"/>
-      <c r="I89" s="12"/>
-      <c r="J89" s="12"/>
-      <c r="K89" s="12"/>
-      <c r="L89" s="12"/>
+      <c r="G89" s="6"/>
+      <c r="H89" s="6"/>
+      <c r="I89" s="6"/>
+      <c r="J89" s="6"/>
+      <c r="K89" s="6"/>
+      <c r="L89" s="6"/>
     </row>
     <row r="91" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C91" s="6" t="s">
+      <c r="C91" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D91" s="7"/>
-      <c r="E91" s="8"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="15"/>
       <c r="F91" s="5"/>
-      <c r="G91" s="9" t="s">
+      <c r="G91" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H91" s="10"/>
-      <c r="I91" s="10"/>
-      <c r="J91" s="10"/>
-      <c r="K91" s="10"/>
-      <c r="L91" s="11"/>
+      <c r="H91" s="17"/>
+      <c r="I91" s="17"/>
+      <c r="J91" s="17"/>
+      <c r="K91" s="17"/>
+      <c r="L91" s="18"/>
     </row>
     <row r="92" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
-      <c r="G92" s="12"/>
-      <c r="H92" s="12"/>
-      <c r="I92" s="12"/>
-      <c r="J92" s="12"/>
-      <c r="K92" s="12"/>
-      <c r="L92" s="12"/>
+      <c r="G92" s="6"/>
+      <c r="H92" s="6"/>
+      <c r="I92" s="6"/>
+      <c r="J92" s="6"/>
+      <c r="K92" s="6"/>
+      <c r="L92" s="6"/>
     </row>
     <row r="93" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
-      <c r="G93" s="12"/>
-      <c r="H93" s="12"/>
-      <c r="I93" s="12"/>
-      <c r="J93" s="12"/>
-      <c r="K93" s="12"/>
-      <c r="L93" s="12"/>
+      <c r="G93" s="6"/>
+      <c r="H93" s="6"/>
+      <c r="I93" s="6"/>
+      <c r="J93" s="6"/>
+      <c r="K93" s="6"/>
+      <c r="L93" s="6"/>
     </row>
     <row r="94" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G94" s="12"/>
-      <c r="H94" s="12"/>
-      <c r="I94" s="12"/>
-      <c r="J94" s="12"/>
-      <c r="K94" s="12"/>
-      <c r="L94" s="12"/>
+      <c r="G94" s="6"/>
+      <c r="H94" s="6"/>
+      <c r="I94" s="6"/>
+      <c r="J94" s="6"/>
+      <c r="K94" s="6"/>
+      <c r="L94" s="6"/>
     </row>
     <row r="96" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C96" s="6" t="s">
+      <c r="C96" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D96" s="7"/>
-      <c r="E96" s="8"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="15"/>
       <c r="F96" s="5"/>
-      <c r="G96" s="9" t="s">
+      <c r="G96" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H96" s="10"/>
-      <c r="I96" s="10"/>
-      <c r="J96" s="10"/>
-      <c r="K96" s="10"/>
-      <c r="L96" s="11"/>
+      <c r="H96" s="17"/>
+      <c r="I96" s="17"/>
+      <c r="J96" s="17"/>
+      <c r="K96" s="17"/>
+      <c r="L96" s="18"/>
     </row>
     <row r="97" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
-      <c r="G97" s="12"/>
-      <c r="H97" s="12"/>
-      <c r="I97" s="12"/>
-      <c r="J97" s="12"/>
-      <c r="K97" s="12"/>
-      <c r="L97" s="12"/>
+      <c r="G97" s="6"/>
+      <c r="H97" s="6"/>
+      <c r="I97" s="6"/>
+      <c r="J97" s="6"/>
+      <c r="K97" s="6"/>
+      <c r="L97" s="6"/>
     </row>
     <row r="98" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
-      <c r="G98" s="12"/>
-      <c r="H98" s="12"/>
-      <c r="I98" s="12"/>
-      <c r="J98" s="12"/>
-      <c r="K98" s="12"/>
-      <c r="L98" s="12"/>
+      <c r="G98" s="6"/>
+      <c r="H98" s="6"/>
+      <c r="I98" s="6"/>
+      <c r="J98" s="6"/>
+      <c r="K98" s="6"/>
+      <c r="L98" s="6"/>
     </row>
     <row r="99" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G99" s="12"/>
-      <c r="H99" s="12"/>
-      <c r="I99" s="12"/>
-      <c r="J99" s="12"/>
-      <c r="K99" s="12"/>
-      <c r="L99" s="12"/>
+      <c r="G99" s="6"/>
+      <c r="H99" s="6"/>
+      <c r="I99" s="6"/>
+      <c r="J99" s="6"/>
+      <c r="K99" s="6"/>
+      <c r="L99" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="101">
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:W6"/>
+    <mergeCell ref="R7:W7"/>
+    <mergeCell ref="R8:W8"/>
+    <mergeCell ref="R9:W9"/>
+    <mergeCell ref="G82:L82"/>
+    <mergeCell ref="G83:L83"/>
+    <mergeCell ref="G84:L84"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="G86:L86"/>
+    <mergeCell ref="G87:L87"/>
+    <mergeCell ref="G93:L93"/>
+    <mergeCell ref="G94:L94"/>
+    <mergeCell ref="G88:L88"/>
+    <mergeCell ref="G89:L89"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="G91:L91"/>
+    <mergeCell ref="G92:L92"/>
+    <mergeCell ref="G72:L72"/>
+    <mergeCell ref="G73:L73"/>
+    <mergeCell ref="G74:L74"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="G76:L76"/>
+    <mergeCell ref="G77:L77"/>
+    <mergeCell ref="G78:L78"/>
+    <mergeCell ref="G79:L79"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="G81:L81"/>
+    <mergeCell ref="G62:L62"/>
+    <mergeCell ref="G63:L63"/>
+    <mergeCell ref="G64:L64"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="G66:L66"/>
+    <mergeCell ref="G67:L67"/>
+    <mergeCell ref="G68:L68"/>
+    <mergeCell ref="G69:L69"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="G71:L71"/>
+    <mergeCell ref="G52:L52"/>
+    <mergeCell ref="G53:L53"/>
+    <mergeCell ref="G54:L54"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="G56:L56"/>
+    <mergeCell ref="G57:L57"/>
+    <mergeCell ref="G58:L58"/>
+    <mergeCell ref="G59:L59"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="G61:L61"/>
+    <mergeCell ref="G42:L42"/>
+    <mergeCell ref="G43:L43"/>
+    <mergeCell ref="G44:L44"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="G46:L46"/>
+    <mergeCell ref="G47:L47"/>
+    <mergeCell ref="G48:L48"/>
+    <mergeCell ref="G49:L49"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="G51:L51"/>
+    <mergeCell ref="G32:L32"/>
+    <mergeCell ref="G33:L33"/>
+    <mergeCell ref="G34:L34"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="G36:L36"/>
+    <mergeCell ref="G37:L37"/>
+    <mergeCell ref="G38:L38"/>
+    <mergeCell ref="G39:L39"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="G41:L41"/>
+    <mergeCell ref="G23:L23"/>
+    <mergeCell ref="G24:L24"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="G26:L26"/>
+    <mergeCell ref="G27:L27"/>
+    <mergeCell ref="G28:L28"/>
+    <mergeCell ref="G29:L29"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="G31:L31"/>
     <mergeCell ref="G99:L99"/>
     <mergeCell ref="G2:L3"/>
     <mergeCell ref="C96:E96"/>
@@ -1821,83 +1903,6 @@
     <mergeCell ref="C21:E21"/>
     <mergeCell ref="G21:L21"/>
     <mergeCell ref="G22:L22"/>
-    <mergeCell ref="G23:L23"/>
-    <mergeCell ref="G24:L24"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="G26:L26"/>
-    <mergeCell ref="G27:L27"/>
-    <mergeCell ref="G28:L28"/>
-    <mergeCell ref="G29:L29"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="G31:L31"/>
-    <mergeCell ref="G32:L32"/>
-    <mergeCell ref="G33:L33"/>
-    <mergeCell ref="G34:L34"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="G36:L36"/>
-    <mergeCell ref="G37:L37"/>
-    <mergeCell ref="G38:L38"/>
-    <mergeCell ref="G39:L39"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="G41:L41"/>
-    <mergeCell ref="G42:L42"/>
-    <mergeCell ref="G43:L43"/>
-    <mergeCell ref="G44:L44"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="G46:L46"/>
-    <mergeCell ref="G47:L47"/>
-    <mergeCell ref="G48:L48"/>
-    <mergeCell ref="G49:L49"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="G51:L51"/>
-    <mergeCell ref="G52:L52"/>
-    <mergeCell ref="G53:L53"/>
-    <mergeCell ref="G54:L54"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="G56:L56"/>
-    <mergeCell ref="G57:L57"/>
-    <mergeCell ref="G58:L58"/>
-    <mergeCell ref="G59:L59"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="G61:L61"/>
-    <mergeCell ref="G62:L62"/>
-    <mergeCell ref="G63:L63"/>
-    <mergeCell ref="G64:L64"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="G66:L66"/>
-    <mergeCell ref="G67:L67"/>
-    <mergeCell ref="G68:L68"/>
-    <mergeCell ref="G69:L69"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="G71:L71"/>
-    <mergeCell ref="G72:L72"/>
-    <mergeCell ref="G73:L73"/>
-    <mergeCell ref="G74:L74"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="G76:L76"/>
-    <mergeCell ref="G77:L77"/>
-    <mergeCell ref="G78:L78"/>
-    <mergeCell ref="G79:L79"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="G81:L81"/>
-    <mergeCell ref="G82:L82"/>
-    <mergeCell ref="G83:L83"/>
-    <mergeCell ref="G84:L84"/>
-    <mergeCell ref="C86:E86"/>
-    <mergeCell ref="G86:L86"/>
-    <mergeCell ref="G87:L87"/>
-    <mergeCell ref="G93:L93"/>
-    <mergeCell ref="G94:L94"/>
-    <mergeCell ref="G88:L88"/>
-    <mergeCell ref="G89:L89"/>
-    <mergeCell ref="C91:E91"/>
-    <mergeCell ref="G91:L91"/>
-    <mergeCell ref="G92:L92"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:W6"/>
-    <mergeCell ref="R7:W7"/>
-    <mergeCell ref="R8:W8"/>
-    <mergeCell ref="R9:W9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data_Structures_and_Algorithms.xlsx
+++ b/Data_Structures_and_Algorithms.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nvjsi\Desktop\My Projects\pro-data-structures-and-algorithms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0A86C4-ED72-442D-BFBE-75A4D7B2EE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B07A9F8-C9DB-403C-9103-3C68EA020FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{463DEBCD-443E-4114-A884-3BF4F43F1855}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="27">
   <si>
     <t>Data Structures and Algorithms</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>binary search</t>
+  </si>
+  <si>
+    <t>include and exclude</t>
   </si>
 </sst>
 </file>
@@ -393,6 +396,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -412,24 +433,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -799,23 +802,33 @@
     <col min="3" max="5" width="10.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="G2" s="7" t="s">
+    <row r="2" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="9"/>
-    </row>
-    <row r="3" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="G3" s="10"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="12"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="15"/>
+    </row>
+    <row r="3" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G3" s="16"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="18"/>
     </row>
     <row r="5" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2"/>
@@ -836,35 +849,35 @@
     </row>
     <row r="6" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="1"/>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="15"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="8"/>
       <c r="F6" s="5"/>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="18"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="11"/>
       <c r="M6" s="1"/>
-      <c r="N6" s="13" t="s">
+      <c r="N6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="O6" s="14"/>
-      <c r="P6" s="15"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="8"/>
       <c r="Q6" s="5"/>
-      <c r="R6" s="16" t="s">
+      <c r="R6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="S6" s="17"/>
-      <c r="T6" s="17"/>
-      <c r="U6" s="17"/>
-      <c r="V6" s="17"/>
-      <c r="W6" s="18"/>
+      <c r="S6" s="10"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+      <c r="V6" s="10"/>
+      <c r="W6" s="11"/>
     </row>
     <row r="7" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1"/>
@@ -872,25 +885,25 @@
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
       <c r="M7" s="1"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="12"/>
+      <c r="V7" s="12"/>
+      <c r="W7" s="12"/>
     </row>
     <row r="8" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1"/>
@@ -898,85 +911,85 @@
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
       <c r="M8" s="1"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="12"/>
+      <c r="V8" s="12"/>
+      <c r="W8" s="12"/>
     </row>
     <row r="9" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
-      <c r="T9" s="6"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="6"/>
-      <c r="W9" s="6"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="12"/>
+      <c r="U9" s="12"/>
+      <c r="V9" s="12"/>
+      <c r="W9" s="12"/>
     </row>
     <row r="11" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="15"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="8"/>
       <c r="F11" s="5"/>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="18"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="11"/>
     </row>
     <row r="12" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
     </row>
     <row r="13" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
     </row>
     <row r="14" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
     </row>
     <row r="16" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C16" s="19" t="s">
@@ -999,32 +1012,32 @@
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
     </row>
     <row r="21" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C21" s="19" t="s">
@@ -1047,840 +1060,765 @@
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="14"/>
-      <c r="E26" s="15"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="8"/>
       <c r="F26" s="5"/>
-      <c r="G26" s="16" t="s">
+      <c r="G26" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="18"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="11"/>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
     </row>
     <row r="28" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
     </row>
     <row r="29" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="14"/>
-      <c r="E31" s="15"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="8"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="16" t="s">
+      <c r="G31" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="18"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="11"/>
     </row>
     <row r="32" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
     </row>
     <row r="36" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D36" s="14"/>
-      <c r="E36" s="15"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="8"/>
       <c r="F36" s="5"/>
-      <c r="G36" s="16" t="s">
+      <c r="G36" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="18"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="11"/>
     </row>
     <row r="37" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="6"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="12"/>
     </row>
     <row r="38" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12"/>
+      <c r="K38" s="12"/>
+      <c r="L38" s="12"/>
     </row>
     <row r="39" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="12"/>
+      <c r="K39" s="12"/>
+      <c r="L39" s="12"/>
     </row>
     <row r="41" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="14"/>
-      <c r="E41" s="15"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="8"/>
       <c r="F41" s="5"/>
-      <c r="G41" s="16" t="s">
+      <c r="G41" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="18"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="11"/>
     </row>
     <row r="42" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="6"/>
-      <c r="L42" s="6"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+      <c r="I42" s="12"/>
+      <c r="J42" s="12"/>
+      <c r="K42" s="12"/>
+      <c r="L42" s="12"/>
     </row>
     <row r="43" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6"/>
-      <c r="L43" s="6"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12"/>
+      <c r="L43" s="12"/>
     </row>
     <row r="44" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="12"/>
+      <c r="K44" s="12"/>
+      <c r="L44" s="12"/>
     </row>
     <row r="46" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="14"/>
-      <c r="E46" s="15"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="8"/>
       <c r="F46" s="5"/>
-      <c r="G46" s="16" t="s">
+      <c r="G46" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H46" s="17"/>
-      <c r="I46" s="17"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="17"/>
-      <c r="L46" s="18"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="11"/>
     </row>
     <row r="47" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="6"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="12"/>
+      <c r="K47" s="12"/>
+      <c r="L47" s="12"/>
     </row>
     <row r="48" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="12"/>
+      <c r="L48" s="12"/>
     </row>
     <row r="49" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="6"/>
-      <c r="L49" s="6"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
+      <c r="I49" s="12"/>
+      <c r="J49" s="12"/>
+      <c r="K49" s="12"/>
+      <c r="L49" s="12"/>
     </row>
     <row r="51" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C51" s="13" t="s">
+      <c r="C51" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="15"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="8"/>
       <c r="F51" s="5"/>
-      <c r="G51" s="16" t="s">
+      <c r="G51" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H51" s="17"/>
-      <c r="I51" s="17"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="18"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="11"/>
     </row>
     <row r="52" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="6"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
+      <c r="I52" s="12"/>
+      <c r="J52" s="12"/>
+      <c r="K52" s="12"/>
+      <c r="L52" s="12"/>
     </row>
     <row r="53" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="6"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="12"/>
+      <c r="I53" s="12"/>
+      <c r="J53" s="12"/>
+      <c r="K53" s="12"/>
+      <c r="L53" s="12"/>
     </row>
     <row r="54" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="6"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="12"/>
+      <c r="J54" s="12"/>
+      <c r="K54" s="12"/>
+      <c r="L54" s="12"/>
     </row>
     <row r="56" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C56" s="13" t="s">
+      <c r="C56" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D56" s="14"/>
-      <c r="E56" s="15"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="8"/>
       <c r="F56" s="5"/>
-      <c r="G56" s="16" t="s">
+      <c r="G56" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H56" s="17"/>
-      <c r="I56" s="17"/>
-      <c r="J56" s="17"/>
-      <c r="K56" s="17"/>
-      <c r="L56" s="18"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
+      <c r="K56" s="10"/>
+      <c r="L56" s="11"/>
     </row>
     <row r="57" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="6"/>
-      <c r="K57" s="6"/>
-      <c r="L57" s="6"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
+      <c r="I57" s="12"/>
+      <c r="J57" s="12"/>
+      <c r="K57" s="12"/>
+      <c r="L57" s="12"/>
     </row>
     <row r="58" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="6"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="12"/>
+      <c r="I58" s="12"/>
+      <c r="J58" s="12"/>
+      <c r="K58" s="12"/>
+      <c r="L58" s="12"/>
     </row>
     <row r="59" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="12"/>
+      <c r="I59" s="12"/>
+      <c r="J59" s="12"/>
+      <c r="K59" s="12"/>
+      <c r="L59" s="12"/>
     </row>
     <row r="61" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C61" s="13" t="s">
+      <c r="C61" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D61" s="14"/>
-      <c r="E61" s="15"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="8"/>
       <c r="F61" s="5"/>
-      <c r="G61" s="16" t="s">
+      <c r="G61" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H61" s="17"/>
-      <c r="I61" s="17"/>
-      <c r="J61" s="17"/>
-      <c r="K61" s="17"/>
-      <c r="L61" s="18"/>
+      <c r="H61" s="10"/>
+      <c r="I61" s="10"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="10"/>
+      <c r="L61" s="11"/>
     </row>
     <row r="62" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6"/>
-      <c r="L62" s="6"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="12"/>
+      <c r="J62" s="12"/>
+      <c r="K62" s="12"/>
+      <c r="L62" s="12"/>
     </row>
     <row r="63" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="6"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12"/>
+      <c r="I63" s="12"/>
+      <c r="J63" s="12"/>
+      <c r="K63" s="12"/>
+      <c r="L63" s="12"/>
     </row>
     <row r="64" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6"/>
-      <c r="J64" s="6"/>
-      <c r="K64" s="6"/>
-      <c r="L64" s="6"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12"/>
+      <c r="I64" s="12"/>
+      <c r="J64" s="12"/>
+      <c r="K64" s="12"/>
+      <c r="L64" s="12"/>
     </row>
     <row r="66" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C66" s="13" t="s">
+      <c r="C66" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D66" s="14"/>
-      <c r="E66" s="15"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="8"/>
       <c r="F66" s="5"/>
-      <c r="G66" s="16" t="s">
+      <c r="G66" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H66" s="17"/>
-      <c r="I66" s="17"/>
-      <c r="J66" s="17"/>
-      <c r="K66" s="17"/>
-      <c r="L66" s="18"/>
+      <c r="H66" s="10"/>
+      <c r="I66" s="10"/>
+      <c r="J66" s="10"/>
+      <c r="K66" s="10"/>
+      <c r="L66" s="11"/>
     </row>
     <row r="67" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
-      <c r="G67" s="6"/>
-      <c r="H67" s="6"/>
-      <c r="I67" s="6"/>
-      <c r="J67" s="6"/>
-      <c r="K67" s="6"/>
-      <c r="L67" s="6"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="12"/>
+      <c r="I67" s="12"/>
+      <c r="J67" s="12"/>
+      <c r="K67" s="12"/>
+      <c r="L67" s="12"/>
     </row>
     <row r="68" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="6"/>
-      <c r="J68" s="6"/>
-      <c r="K68" s="6"/>
-      <c r="L68" s="6"/>
+      <c r="G68" s="12"/>
+      <c r="H68" s="12"/>
+      <c r="I68" s="12"/>
+      <c r="J68" s="12"/>
+      <c r="K68" s="12"/>
+      <c r="L68" s="12"/>
     </row>
     <row r="69" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G69" s="6"/>
-      <c r="H69" s="6"/>
-      <c r="I69" s="6"/>
-      <c r="J69" s="6"/>
-      <c r="K69" s="6"/>
-      <c r="L69" s="6"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="12"/>
+      <c r="I69" s="12"/>
+      <c r="J69" s="12"/>
+      <c r="K69" s="12"/>
+      <c r="L69" s="12"/>
     </row>
     <row r="71" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C71" s="13" t="s">
+      <c r="C71" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D71" s="14"/>
-      <c r="E71" s="15"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="8"/>
       <c r="F71" s="5"/>
-      <c r="G71" s="16" t="s">
+      <c r="G71" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H71" s="17"/>
-      <c r="I71" s="17"/>
-      <c r="J71" s="17"/>
-      <c r="K71" s="17"/>
-      <c r="L71" s="18"/>
+      <c r="H71" s="10"/>
+      <c r="I71" s="10"/>
+      <c r="J71" s="10"/>
+      <c r="K71" s="10"/>
+      <c r="L71" s="11"/>
     </row>
     <row r="72" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
-      <c r="J72" s="6"/>
-      <c r="K72" s="6"/>
-      <c r="L72" s="6"/>
+      <c r="G72" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H72" s="12"/>
+      <c r="I72" s="12"/>
+      <c r="J72" s="12"/>
+      <c r="K72" s="12"/>
+      <c r="L72" s="12"/>
     </row>
     <row r="73" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
-      <c r="G73" s="6"/>
-      <c r="H73" s="6"/>
-      <c r="I73" s="6"/>
-      <c r="J73" s="6"/>
-      <c r="K73" s="6"/>
-      <c r="L73" s="6"/>
+      <c r="G73" s="12"/>
+      <c r="H73" s="12"/>
+      <c r="I73" s="12"/>
+      <c r="J73" s="12"/>
+      <c r="K73" s="12"/>
+      <c r="L73" s="12"/>
     </row>
     <row r="74" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
-      <c r="L74" s="6"/>
+      <c r="G74" s="12"/>
+      <c r="H74" s="12"/>
+      <c r="I74" s="12"/>
+      <c r="J74" s="12"/>
+      <c r="K74" s="12"/>
+      <c r="L74" s="12"/>
     </row>
     <row r="76" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C76" s="13" t="s">
+      <c r="C76" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D76" s="14"/>
-      <c r="E76" s="15"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="8"/>
       <c r="F76" s="5"/>
-      <c r="G76" s="16" t="s">
+      <c r="G76" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H76" s="17"/>
-      <c r="I76" s="17"/>
-      <c r="J76" s="17"/>
-      <c r="K76" s="17"/>
-      <c r="L76" s="18"/>
+      <c r="H76" s="10"/>
+      <c r="I76" s="10"/>
+      <c r="J76" s="10"/>
+      <c r="K76" s="10"/>
+      <c r="L76" s="11"/>
     </row>
     <row r="77" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
-      <c r="G77" s="6" t="s">
+      <c r="G77" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="H77" s="6"/>
-      <c r="I77" s="6"/>
-      <c r="J77" s="6"/>
-      <c r="K77" s="6"/>
-      <c r="L77" s="6"/>
+      <c r="H77" s="12"/>
+      <c r="I77" s="12"/>
+      <c r="J77" s="12"/>
+      <c r="K77" s="12"/>
+      <c r="L77" s="12"/>
     </row>
     <row r="78" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
-      <c r="G78" s="6"/>
-      <c r="H78" s="6"/>
-      <c r="I78" s="6"/>
-      <c r="J78" s="6"/>
-      <c r="K78" s="6"/>
-      <c r="L78" s="6"/>
+      <c r="G78" s="12"/>
+      <c r="H78" s="12"/>
+      <c r="I78" s="12"/>
+      <c r="J78" s="12"/>
+      <c r="K78" s="12"/>
+      <c r="L78" s="12"/>
     </row>
     <row r="79" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G79" s="6"/>
-      <c r="H79" s="6"/>
-      <c r="I79" s="6"/>
-      <c r="J79" s="6"/>
-      <c r="K79" s="6"/>
-      <c r="L79" s="6"/>
+      <c r="G79" s="12"/>
+      <c r="H79" s="12"/>
+      <c r="I79" s="12"/>
+      <c r="J79" s="12"/>
+      <c r="K79" s="12"/>
+      <c r="L79" s="12"/>
     </row>
     <row r="81" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C81" s="13" t="s">
+      <c r="C81" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D81" s="14"/>
-      <c r="E81" s="15"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="8"/>
       <c r="F81" s="5"/>
-      <c r="G81" s="16" t="s">
+      <c r="G81" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H81" s="17"/>
-      <c r="I81" s="17"/>
-      <c r="J81" s="17"/>
-      <c r="K81" s="17"/>
-      <c r="L81" s="18"/>
+      <c r="H81" s="10"/>
+      <c r="I81" s="10"/>
+      <c r="J81" s="10"/>
+      <c r="K81" s="10"/>
+      <c r="L81" s="11"/>
     </row>
     <row r="82" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
-      <c r="G82" s="6"/>
-      <c r="H82" s="6"/>
-      <c r="I82" s="6"/>
-      <c r="J82" s="6"/>
-      <c r="K82" s="6"/>
-      <c r="L82" s="6"/>
+      <c r="G82" s="12"/>
+      <c r="H82" s="12"/>
+      <c r="I82" s="12"/>
+      <c r="J82" s="12"/>
+      <c r="K82" s="12"/>
+      <c r="L82" s="12"/>
     </row>
     <row r="83" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
-      <c r="G83" s="6"/>
-      <c r="H83" s="6"/>
-      <c r="I83" s="6"/>
-      <c r="J83" s="6"/>
-      <c r="K83" s="6"/>
-      <c r="L83" s="6"/>
+      <c r="G83" s="12"/>
+      <c r="H83" s="12"/>
+      <c r="I83" s="12"/>
+      <c r="J83" s="12"/>
+      <c r="K83" s="12"/>
+      <c r="L83" s="12"/>
     </row>
     <row r="84" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G84" s="6"/>
-      <c r="H84" s="6"/>
-      <c r="I84" s="6"/>
-      <c r="J84" s="6"/>
-      <c r="K84" s="6"/>
-      <c r="L84" s="6"/>
+      <c r="G84" s="12"/>
+      <c r="H84" s="12"/>
+      <c r="I84" s="12"/>
+      <c r="J84" s="12"/>
+      <c r="K84" s="12"/>
+      <c r="L84" s="12"/>
     </row>
     <row r="86" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C86" s="13" t="s">
+      <c r="C86" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D86" s="14"/>
-      <c r="E86" s="15"/>
+      <c r="D86" s="7"/>
+      <c r="E86" s="8"/>
       <c r="F86" s="5"/>
-      <c r="G86" s="16" t="s">
+      <c r="G86" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H86" s="17"/>
-      <c r="I86" s="17"/>
-      <c r="J86" s="17"/>
-      <c r="K86" s="17"/>
-      <c r="L86" s="18"/>
+      <c r="H86" s="10"/>
+      <c r="I86" s="10"/>
+      <c r="J86" s="10"/>
+      <c r="K86" s="10"/>
+      <c r="L86" s="11"/>
     </row>
     <row r="87" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
-      <c r="G87" s="6" t="s">
+      <c r="G87" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H87" s="6"/>
-      <c r="I87" s="6"/>
-      <c r="J87" s="6"/>
-      <c r="K87" s="6"/>
-      <c r="L87" s="6"/>
+      <c r="H87" s="12"/>
+      <c r="I87" s="12"/>
+      <c r="J87" s="12"/>
+      <c r="K87" s="12"/>
+      <c r="L87" s="12"/>
     </row>
     <row r="88" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
-      <c r="G88" s="6"/>
-      <c r="H88" s="6"/>
-      <c r="I88" s="6"/>
-      <c r="J88" s="6"/>
-      <c r="K88" s="6"/>
-      <c r="L88" s="6"/>
+      <c r="G88" s="12"/>
+      <c r="H88" s="12"/>
+      <c r="I88" s="12"/>
+      <c r="J88" s="12"/>
+      <c r="K88" s="12"/>
+      <c r="L88" s="12"/>
     </row>
     <row r="89" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G89" s="6"/>
-      <c r="H89" s="6"/>
-      <c r="I89" s="6"/>
-      <c r="J89" s="6"/>
-      <c r="K89" s="6"/>
-      <c r="L89" s="6"/>
+      <c r="G89" s="12"/>
+      <c r="H89" s="12"/>
+      <c r="I89" s="12"/>
+      <c r="J89" s="12"/>
+      <c r="K89" s="12"/>
+      <c r="L89" s="12"/>
     </row>
     <row r="91" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C91" s="13" t="s">
+      <c r="C91" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D91" s="14"/>
-      <c r="E91" s="15"/>
+      <c r="D91" s="7"/>
+      <c r="E91" s="8"/>
       <c r="F91" s="5"/>
-      <c r="G91" s="16" t="s">
+      <c r="G91" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H91" s="17"/>
-      <c r="I91" s="17"/>
-      <c r="J91" s="17"/>
-      <c r="K91" s="17"/>
-      <c r="L91" s="18"/>
+      <c r="H91" s="10"/>
+      <c r="I91" s="10"/>
+      <c r="J91" s="10"/>
+      <c r="K91" s="10"/>
+      <c r="L91" s="11"/>
     </row>
     <row r="92" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
-      <c r="G92" s="6"/>
-      <c r="H92" s="6"/>
-      <c r="I92" s="6"/>
-      <c r="J92" s="6"/>
-      <c r="K92" s="6"/>
-      <c r="L92" s="6"/>
+      <c r="G92" s="12"/>
+      <c r="H92" s="12"/>
+      <c r="I92" s="12"/>
+      <c r="J92" s="12"/>
+      <c r="K92" s="12"/>
+      <c r="L92" s="12"/>
     </row>
     <row r="93" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
-      <c r="G93" s="6"/>
-      <c r="H93" s="6"/>
-      <c r="I93" s="6"/>
-      <c r="J93" s="6"/>
-      <c r="K93" s="6"/>
-      <c r="L93" s="6"/>
+      <c r="G93" s="12"/>
+      <c r="H93" s="12"/>
+      <c r="I93" s="12"/>
+      <c r="J93" s="12"/>
+      <c r="K93" s="12"/>
+      <c r="L93" s="12"/>
     </row>
     <row r="94" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G94" s="6"/>
-      <c r="H94" s="6"/>
-      <c r="I94" s="6"/>
-      <c r="J94" s="6"/>
-      <c r="K94" s="6"/>
-      <c r="L94" s="6"/>
+      <c r="G94" s="12"/>
+      <c r="H94" s="12"/>
+      <c r="I94" s="12"/>
+      <c r="J94" s="12"/>
+      <c r="K94" s="12"/>
+      <c r="L94" s="12"/>
     </row>
     <row r="96" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C96" s="13" t="s">
+      <c r="C96" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D96" s="14"/>
-      <c r="E96" s="15"/>
+      <c r="D96" s="7"/>
+      <c r="E96" s="8"/>
       <c r="F96" s="5"/>
-      <c r="G96" s="16" t="s">
+      <c r="G96" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H96" s="17"/>
-      <c r="I96" s="17"/>
-      <c r="J96" s="17"/>
-      <c r="K96" s="17"/>
-      <c r="L96" s="18"/>
+      <c r="H96" s="10"/>
+      <c r="I96" s="10"/>
+      <c r="J96" s="10"/>
+      <c r="K96" s="10"/>
+      <c r="L96" s="11"/>
     </row>
     <row r="97" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
-      <c r="G97" s="6"/>
-      <c r="H97" s="6"/>
-      <c r="I97" s="6"/>
-      <c r="J97" s="6"/>
-      <c r="K97" s="6"/>
-      <c r="L97" s="6"/>
+      <c r="G97" s="12"/>
+      <c r="H97" s="12"/>
+      <c r="I97" s="12"/>
+      <c r="J97" s="12"/>
+      <c r="K97" s="12"/>
+      <c r="L97" s="12"/>
     </row>
     <row r="98" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
-      <c r="G98" s="6"/>
-      <c r="H98" s="6"/>
-      <c r="I98" s="6"/>
-      <c r="J98" s="6"/>
-      <c r="K98" s="6"/>
-      <c r="L98" s="6"/>
+      <c r="G98" s="12"/>
+      <c r="H98" s="12"/>
+      <c r="I98" s="12"/>
+      <c r="J98" s="12"/>
+      <c r="K98" s="12"/>
+      <c r="L98" s="12"/>
     </row>
     <row r="99" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G99" s="6"/>
-      <c r="H99" s="6"/>
-      <c r="I99" s="6"/>
-      <c r="J99" s="6"/>
-      <c r="K99" s="6"/>
-      <c r="L99" s="6"/>
+      <c r="G99" s="12"/>
+      <c r="H99" s="12"/>
+      <c r="I99" s="12"/>
+      <c r="J99" s="12"/>
+      <c r="K99" s="12"/>
+      <c r="L99" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="101">
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:W6"/>
-    <mergeCell ref="R7:W7"/>
-    <mergeCell ref="R8:W8"/>
-    <mergeCell ref="R9:W9"/>
-    <mergeCell ref="G82:L82"/>
-    <mergeCell ref="G83:L83"/>
-    <mergeCell ref="G84:L84"/>
-    <mergeCell ref="C86:E86"/>
-    <mergeCell ref="G86:L86"/>
-    <mergeCell ref="G87:L87"/>
-    <mergeCell ref="G93:L93"/>
-    <mergeCell ref="G94:L94"/>
-    <mergeCell ref="G88:L88"/>
-    <mergeCell ref="G89:L89"/>
-    <mergeCell ref="C91:E91"/>
-    <mergeCell ref="G91:L91"/>
-    <mergeCell ref="G92:L92"/>
-    <mergeCell ref="G72:L72"/>
-    <mergeCell ref="G73:L73"/>
-    <mergeCell ref="G74:L74"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="G76:L76"/>
-    <mergeCell ref="G77:L77"/>
-    <mergeCell ref="G78:L78"/>
-    <mergeCell ref="G79:L79"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="G81:L81"/>
-    <mergeCell ref="G62:L62"/>
-    <mergeCell ref="G63:L63"/>
-    <mergeCell ref="G64:L64"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="G66:L66"/>
-    <mergeCell ref="G67:L67"/>
-    <mergeCell ref="G68:L68"/>
-    <mergeCell ref="G69:L69"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="G71:L71"/>
-    <mergeCell ref="G52:L52"/>
-    <mergeCell ref="G53:L53"/>
-    <mergeCell ref="G54:L54"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="G56:L56"/>
-    <mergeCell ref="G57:L57"/>
-    <mergeCell ref="G58:L58"/>
-    <mergeCell ref="G59:L59"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="G61:L61"/>
-    <mergeCell ref="G42:L42"/>
-    <mergeCell ref="G43:L43"/>
-    <mergeCell ref="G44:L44"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="G46:L46"/>
-    <mergeCell ref="G47:L47"/>
-    <mergeCell ref="G48:L48"/>
-    <mergeCell ref="G49:L49"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="G51:L51"/>
-    <mergeCell ref="G32:L32"/>
-    <mergeCell ref="G33:L33"/>
-    <mergeCell ref="G34:L34"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="G36:L36"/>
-    <mergeCell ref="G37:L37"/>
-    <mergeCell ref="G38:L38"/>
-    <mergeCell ref="G39:L39"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="G41:L41"/>
-    <mergeCell ref="G23:L23"/>
-    <mergeCell ref="G24:L24"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="G26:L26"/>
-    <mergeCell ref="G27:L27"/>
-    <mergeCell ref="G28:L28"/>
-    <mergeCell ref="G29:L29"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="G31:L31"/>
+    <mergeCell ref="G2:Q3"/>
     <mergeCell ref="G99:L99"/>
-    <mergeCell ref="G2:L3"/>
     <mergeCell ref="C96:E96"/>
     <mergeCell ref="G96:L96"/>
     <mergeCell ref="G97:L97"/>
@@ -1903,6 +1841,83 @@
     <mergeCell ref="C21:E21"/>
     <mergeCell ref="G21:L21"/>
     <mergeCell ref="G22:L22"/>
+    <mergeCell ref="G23:L23"/>
+    <mergeCell ref="G24:L24"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="G26:L26"/>
+    <mergeCell ref="G27:L27"/>
+    <mergeCell ref="G28:L28"/>
+    <mergeCell ref="G29:L29"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="G31:L31"/>
+    <mergeCell ref="G32:L32"/>
+    <mergeCell ref="G33:L33"/>
+    <mergeCell ref="G34:L34"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="G36:L36"/>
+    <mergeCell ref="G37:L37"/>
+    <mergeCell ref="G38:L38"/>
+    <mergeCell ref="G39:L39"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="G41:L41"/>
+    <mergeCell ref="G56:L56"/>
+    <mergeCell ref="G57:L57"/>
+    <mergeCell ref="G58:L58"/>
+    <mergeCell ref="G59:L59"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="G61:L61"/>
+    <mergeCell ref="G42:L42"/>
+    <mergeCell ref="G43:L43"/>
+    <mergeCell ref="G44:L44"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="G46:L46"/>
+    <mergeCell ref="G47:L47"/>
+    <mergeCell ref="G48:L48"/>
+    <mergeCell ref="G49:L49"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="G51:L51"/>
+    <mergeCell ref="G87:L87"/>
+    <mergeCell ref="G93:L93"/>
+    <mergeCell ref="G94:L94"/>
+    <mergeCell ref="G88:L88"/>
+    <mergeCell ref="G89:L89"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="G91:L91"/>
+    <mergeCell ref="G92:L92"/>
+    <mergeCell ref="G72:L72"/>
+    <mergeCell ref="G73:L73"/>
+    <mergeCell ref="G74:L74"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="G76:L76"/>
+    <mergeCell ref="G77:L77"/>
+    <mergeCell ref="G78:L78"/>
+    <mergeCell ref="G79:L79"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="G81:L81"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:W6"/>
+    <mergeCell ref="R7:W7"/>
+    <mergeCell ref="R8:W8"/>
+    <mergeCell ref="R9:W9"/>
+    <mergeCell ref="G82:L82"/>
+    <mergeCell ref="G83:L83"/>
+    <mergeCell ref="G84:L84"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="G86:L86"/>
+    <mergeCell ref="G62:L62"/>
+    <mergeCell ref="G63:L63"/>
+    <mergeCell ref="G64:L64"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="G66:L66"/>
+    <mergeCell ref="G67:L67"/>
+    <mergeCell ref="G68:L68"/>
+    <mergeCell ref="G69:L69"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="G71:L71"/>
+    <mergeCell ref="G52:L52"/>
+    <mergeCell ref="G53:L53"/>
+    <mergeCell ref="G54:L54"/>
+    <mergeCell ref="C56:E56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data_Structures_and_Algorithms.xlsx
+++ b/Data_Structures_and_Algorithms.xlsx
@@ -1,42 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nvjsi\Desktop\My Projects\pro-data-structures-and-algorithms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B07A9F8-C9DB-403C-9103-3C68EA020FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{109ADAFE-4D99-4F56-B413-B787B1AC6BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{463DEBCD-443E-4114-A884-3BF4F43F1855}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="28">
   <si>
     <t>Data Structures and Algorithms</t>
   </si>
@@ -117,6 +106,9 @@
   </si>
   <si>
     <t>include and exclude</t>
+  </si>
+  <si>
+    <t>merge interval</t>
   </si>
 </sst>
 </file>
@@ -396,6 +388,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -412,27 +425,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -803,32 +795,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="15"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="8"/>
     </row>
     <row r="3" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G3" s="16"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="18"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="11"/>
     </row>
     <row r="5" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2"/>
@@ -849,35 +841,35 @@
     </row>
     <row r="6" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="1"/>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="15"/>
       <c r="F6" s="5"/>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="11"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="18"/>
       <c r="M6" s="1"/>
-      <c r="N6" s="6" t="s">
+      <c r="N6" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="O6" s="7"/>
-      <c r="P6" s="8"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="15"/>
       <c r="Q6" s="5"/>
-      <c r="R6" s="9" t="s">
+      <c r="R6" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="S6" s="10"/>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10"/>
-      <c r="V6" s="10"/>
-      <c r="W6" s="11"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="18"/>
     </row>
     <row r="7" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1"/>
@@ -944,20 +936,20 @@
       <c r="W9" s="12"/>
     </row>
     <row r="11" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="8"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="15"/>
       <c r="F11" s="5"/>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="11"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="18"/>
     </row>
     <row r="12" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C12" s="3"/>
@@ -1088,20 +1080,20 @@
       <c r="L24" s="12"/>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="7"/>
-      <c r="E26" s="8"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="15"/>
       <c r="F26" s="5"/>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="11"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="18"/>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C27" s="3"/>
@@ -1138,27 +1130,29 @@
       <c r="L29" s="12"/>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="7"/>
-      <c r="E31" s="8"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="15"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="9" t="s">
+      <c r="G31" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="11"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="18"/>
     </row>
     <row r="32" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="12"/>
+      <c r="G32" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
       <c r="J32" s="12"/>
@@ -1186,20 +1180,20 @@
       <c r="L34" s="12"/>
     </row>
     <row r="36" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D36" s="7"/>
-      <c r="E36" s="8"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="15"/>
       <c r="F36" s="5"/>
-      <c r="G36" s="9" t="s">
+      <c r="G36" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="11"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="18"/>
     </row>
     <row r="37" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C37" s="3"/>
@@ -1234,20 +1228,20 @@
       <c r="L39" s="12"/>
     </row>
     <row r="41" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="7"/>
-      <c r="E41" s="8"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="15"/>
       <c r="F41" s="5"/>
-      <c r="G41" s="9" t="s">
+      <c r="G41" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="11"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="18"/>
     </row>
     <row r="42" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C42" s="3"/>
@@ -1282,20 +1276,20 @@
       <c r="L44" s="12"/>
     </row>
     <row r="46" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="7"/>
-      <c r="E46" s="8"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="15"/>
       <c r="F46" s="5"/>
-      <c r="G46" s="9" t="s">
+      <c r="G46" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="11"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="18"/>
     </row>
     <row r="47" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C47" s="3"/>
@@ -1330,20 +1324,20 @@
       <c r="L49" s="12"/>
     </row>
     <row r="51" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="7"/>
-      <c r="E51" s="8"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="15"/>
       <c r="F51" s="5"/>
-      <c r="G51" s="9" t="s">
+      <c r="G51" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="11"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="17"/>
+      <c r="J51" s="17"/>
+      <c r="K51" s="17"/>
+      <c r="L51" s="18"/>
     </row>
     <row r="52" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C52" s="3"/>
@@ -1378,20 +1372,20 @@
       <c r="L54" s="12"/>
     </row>
     <row r="56" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D56" s="7"/>
-      <c r="E56" s="8"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="15"/>
       <c r="F56" s="5"/>
-      <c r="G56" s="9" t="s">
+      <c r="G56" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H56" s="10"/>
-      <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
-      <c r="K56" s="10"/>
-      <c r="L56" s="11"/>
+      <c r="H56" s="17"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="17"/>
+      <c r="K56" s="17"/>
+      <c r="L56" s="18"/>
     </row>
     <row r="57" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C57" s="3"/>
@@ -1426,20 +1420,20 @@
       <c r="L59" s="12"/>
     </row>
     <row r="61" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D61" s="7"/>
-      <c r="E61" s="8"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="15"/>
       <c r="F61" s="5"/>
-      <c r="G61" s="9" t="s">
+      <c r="G61" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H61" s="10"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
-      <c r="K61" s="10"/>
-      <c r="L61" s="11"/>
+      <c r="H61" s="17"/>
+      <c r="I61" s="17"/>
+      <c r="J61" s="17"/>
+      <c r="K61" s="17"/>
+      <c r="L61" s="18"/>
     </row>
     <row r="62" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C62" s="3"/>
@@ -1474,20 +1468,20 @@
       <c r="L64" s="12"/>
     </row>
     <row r="66" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D66" s="7"/>
-      <c r="E66" s="8"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="15"/>
       <c r="F66" s="5"/>
-      <c r="G66" s="9" t="s">
+      <c r="G66" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H66" s="10"/>
-      <c r="I66" s="10"/>
-      <c r="J66" s="10"/>
-      <c r="K66" s="10"/>
-      <c r="L66" s="11"/>
+      <c r="H66" s="17"/>
+      <c r="I66" s="17"/>
+      <c r="J66" s="17"/>
+      <c r="K66" s="17"/>
+      <c r="L66" s="18"/>
     </row>
     <row r="67" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C67" s="3"/>
@@ -1522,20 +1516,20 @@
       <c r="L69" s="12"/>
     </row>
     <row r="71" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C71" s="6" t="s">
+      <c r="C71" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D71" s="7"/>
-      <c r="E71" s="8"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="15"/>
       <c r="F71" s="5"/>
-      <c r="G71" s="9" t="s">
+      <c r="G71" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H71" s="10"/>
-      <c r="I71" s="10"/>
-      <c r="J71" s="10"/>
-      <c r="K71" s="10"/>
-      <c r="L71" s="11"/>
+      <c r="H71" s="17"/>
+      <c r="I71" s="17"/>
+      <c r="J71" s="17"/>
+      <c r="K71" s="17"/>
+      <c r="L71" s="18"/>
     </row>
     <row r="72" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C72" s="3"/>
@@ -1572,20 +1566,20 @@
       <c r="L74" s="12"/>
     </row>
     <row r="76" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C76" s="6" t="s">
+      <c r="C76" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D76" s="7"/>
-      <c r="E76" s="8"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="15"/>
       <c r="F76" s="5"/>
-      <c r="G76" s="9" t="s">
+      <c r="G76" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H76" s="10"/>
-      <c r="I76" s="10"/>
-      <c r="J76" s="10"/>
-      <c r="K76" s="10"/>
-      <c r="L76" s="11"/>
+      <c r="H76" s="17"/>
+      <c r="I76" s="17"/>
+      <c r="J76" s="17"/>
+      <c r="K76" s="17"/>
+      <c r="L76" s="18"/>
     </row>
     <row r="77" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C77" s="3"/>
@@ -1622,20 +1616,20 @@
       <c r="L79" s="12"/>
     </row>
     <row r="81" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C81" s="6" t="s">
+      <c r="C81" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D81" s="7"/>
-      <c r="E81" s="8"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="15"/>
       <c r="F81" s="5"/>
-      <c r="G81" s="9" t="s">
+      <c r="G81" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H81" s="10"/>
-      <c r="I81" s="10"/>
-      <c r="J81" s="10"/>
-      <c r="K81" s="10"/>
-      <c r="L81" s="11"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="17"/>
+      <c r="K81" s="17"/>
+      <c r="L81" s="18"/>
     </row>
     <row r="82" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C82" s="3"/>
@@ -1670,20 +1664,20 @@
       <c r="L84" s="12"/>
     </row>
     <row r="86" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C86" s="6" t="s">
+      <c r="C86" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D86" s="7"/>
-      <c r="E86" s="8"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="15"/>
       <c r="F86" s="5"/>
-      <c r="G86" s="9" t="s">
+      <c r="G86" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H86" s="10"/>
-      <c r="I86" s="10"/>
-      <c r="J86" s="10"/>
-      <c r="K86" s="10"/>
-      <c r="L86" s="11"/>
+      <c r="H86" s="17"/>
+      <c r="I86" s="17"/>
+      <c r="J86" s="17"/>
+      <c r="K86" s="17"/>
+      <c r="L86" s="18"/>
     </row>
     <row r="87" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C87" s="3"/>
@@ -1720,20 +1714,20 @@
       <c r="L89" s="12"/>
     </row>
     <row r="91" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C91" s="6" t="s">
+      <c r="C91" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D91" s="7"/>
-      <c r="E91" s="8"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="15"/>
       <c r="F91" s="5"/>
-      <c r="G91" s="9" t="s">
+      <c r="G91" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H91" s="10"/>
-      <c r="I91" s="10"/>
-      <c r="J91" s="10"/>
-      <c r="K91" s="10"/>
-      <c r="L91" s="11"/>
+      <c r="H91" s="17"/>
+      <c r="I91" s="17"/>
+      <c r="J91" s="17"/>
+      <c r="K91" s="17"/>
+      <c r="L91" s="18"/>
     </row>
     <row r="92" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C92" s="3"/>
@@ -1768,20 +1762,20 @@
       <c r="L94" s="12"/>
     </row>
     <row r="96" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C96" s="6" t="s">
+      <c r="C96" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D96" s="7"/>
-      <c r="E96" s="8"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="15"/>
       <c r="F96" s="5"/>
-      <c r="G96" s="9" t="s">
+      <c r="G96" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H96" s="10"/>
-      <c r="I96" s="10"/>
-      <c r="J96" s="10"/>
-      <c r="K96" s="10"/>
-      <c r="L96" s="11"/>
+      <c r="H96" s="17"/>
+      <c r="I96" s="17"/>
+      <c r="J96" s="17"/>
+      <c r="K96" s="17"/>
+      <c r="L96" s="18"/>
     </row>
     <row r="97" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C97" s="3"/>
@@ -1817,6 +1811,83 @@
     </row>
   </sheetData>
   <mergeCells count="101">
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:W6"/>
+    <mergeCell ref="R7:W7"/>
+    <mergeCell ref="R8:W8"/>
+    <mergeCell ref="R9:W9"/>
+    <mergeCell ref="G82:L82"/>
+    <mergeCell ref="G83:L83"/>
+    <mergeCell ref="G84:L84"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="G86:L86"/>
+    <mergeCell ref="G62:L62"/>
+    <mergeCell ref="G63:L63"/>
+    <mergeCell ref="G64:L64"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="G66:L66"/>
+    <mergeCell ref="G67:L67"/>
+    <mergeCell ref="G68:L68"/>
+    <mergeCell ref="G69:L69"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="G71:L71"/>
+    <mergeCell ref="G52:L52"/>
+    <mergeCell ref="G53:L53"/>
+    <mergeCell ref="G54:L54"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="G87:L87"/>
+    <mergeCell ref="G93:L93"/>
+    <mergeCell ref="G94:L94"/>
+    <mergeCell ref="G88:L88"/>
+    <mergeCell ref="G89:L89"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="G91:L91"/>
+    <mergeCell ref="G92:L92"/>
+    <mergeCell ref="G72:L72"/>
+    <mergeCell ref="G73:L73"/>
+    <mergeCell ref="G74:L74"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="G76:L76"/>
+    <mergeCell ref="G77:L77"/>
+    <mergeCell ref="G78:L78"/>
+    <mergeCell ref="G79:L79"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="G81:L81"/>
+    <mergeCell ref="G56:L56"/>
+    <mergeCell ref="G57:L57"/>
+    <mergeCell ref="G58:L58"/>
+    <mergeCell ref="G59:L59"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="G61:L61"/>
+    <mergeCell ref="G42:L42"/>
+    <mergeCell ref="G43:L43"/>
+    <mergeCell ref="G44:L44"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="G46:L46"/>
+    <mergeCell ref="G47:L47"/>
+    <mergeCell ref="G48:L48"/>
+    <mergeCell ref="G49:L49"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="G51:L51"/>
+    <mergeCell ref="G32:L32"/>
+    <mergeCell ref="G33:L33"/>
+    <mergeCell ref="G34:L34"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="G36:L36"/>
+    <mergeCell ref="G37:L37"/>
+    <mergeCell ref="G38:L38"/>
+    <mergeCell ref="G39:L39"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="G41:L41"/>
+    <mergeCell ref="G23:L23"/>
+    <mergeCell ref="G24:L24"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="G26:L26"/>
+    <mergeCell ref="G27:L27"/>
+    <mergeCell ref="G28:L28"/>
+    <mergeCell ref="G29:L29"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="G31:L31"/>
     <mergeCell ref="G2:Q3"/>
     <mergeCell ref="G99:L99"/>
     <mergeCell ref="C96:E96"/>
@@ -1841,83 +1912,6 @@
     <mergeCell ref="C21:E21"/>
     <mergeCell ref="G21:L21"/>
     <mergeCell ref="G22:L22"/>
-    <mergeCell ref="G23:L23"/>
-    <mergeCell ref="G24:L24"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="G26:L26"/>
-    <mergeCell ref="G27:L27"/>
-    <mergeCell ref="G28:L28"/>
-    <mergeCell ref="G29:L29"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="G31:L31"/>
-    <mergeCell ref="G32:L32"/>
-    <mergeCell ref="G33:L33"/>
-    <mergeCell ref="G34:L34"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="G36:L36"/>
-    <mergeCell ref="G37:L37"/>
-    <mergeCell ref="G38:L38"/>
-    <mergeCell ref="G39:L39"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="G41:L41"/>
-    <mergeCell ref="G56:L56"/>
-    <mergeCell ref="G57:L57"/>
-    <mergeCell ref="G58:L58"/>
-    <mergeCell ref="G59:L59"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="G61:L61"/>
-    <mergeCell ref="G42:L42"/>
-    <mergeCell ref="G43:L43"/>
-    <mergeCell ref="G44:L44"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="G46:L46"/>
-    <mergeCell ref="G47:L47"/>
-    <mergeCell ref="G48:L48"/>
-    <mergeCell ref="G49:L49"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="G51:L51"/>
-    <mergeCell ref="G87:L87"/>
-    <mergeCell ref="G93:L93"/>
-    <mergeCell ref="G94:L94"/>
-    <mergeCell ref="G88:L88"/>
-    <mergeCell ref="G89:L89"/>
-    <mergeCell ref="C91:E91"/>
-    <mergeCell ref="G91:L91"/>
-    <mergeCell ref="G92:L92"/>
-    <mergeCell ref="G72:L72"/>
-    <mergeCell ref="G73:L73"/>
-    <mergeCell ref="G74:L74"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="G76:L76"/>
-    <mergeCell ref="G77:L77"/>
-    <mergeCell ref="G78:L78"/>
-    <mergeCell ref="G79:L79"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="G81:L81"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:W6"/>
-    <mergeCell ref="R7:W7"/>
-    <mergeCell ref="R8:W8"/>
-    <mergeCell ref="R9:W9"/>
-    <mergeCell ref="G82:L82"/>
-    <mergeCell ref="G83:L83"/>
-    <mergeCell ref="G84:L84"/>
-    <mergeCell ref="C86:E86"/>
-    <mergeCell ref="G86:L86"/>
-    <mergeCell ref="G62:L62"/>
-    <mergeCell ref="G63:L63"/>
-    <mergeCell ref="G64:L64"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="G66:L66"/>
-    <mergeCell ref="G67:L67"/>
-    <mergeCell ref="G68:L68"/>
-    <mergeCell ref="G69:L69"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="G71:L71"/>
-    <mergeCell ref="G52:L52"/>
-    <mergeCell ref="G53:L53"/>
-    <mergeCell ref="G54:L54"/>
-    <mergeCell ref="C56:E56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data_Structures_and_Algorithms.xlsx
+++ b/Data_Structures_and_Algorithms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nvjsi\Desktop\My Projects\pro-data-structures-and-algorithms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{109ADAFE-4D99-4F56-B413-B787B1AC6BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2957CD65-CFD6-4B95-BB61-F2F8D64EEC90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{463DEBCD-443E-4114-A884-3BF4F43F1855}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="28">
   <si>
     <t>Data Structures and Algorithms</t>
   </si>
@@ -388,6 +388,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -404,27 +425,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -795,32 +795,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="8"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="15"/>
     </row>
     <row r="3" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G3" s="9"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="11"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="18"/>
     </row>
     <row r="5" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2"/>
@@ -841,35 +841,35 @@
     </row>
     <row r="6" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="1"/>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="15"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="8"/>
       <c r="F6" s="5"/>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="18"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="11"/>
       <c r="M6" s="1"/>
-      <c r="N6" s="13" t="s">
+      <c r="N6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="O6" s="14"/>
-      <c r="P6" s="15"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="8"/>
       <c r="Q6" s="5"/>
-      <c r="R6" s="16" t="s">
+      <c r="R6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="S6" s="17"/>
-      <c r="T6" s="17"/>
-      <c r="U6" s="17"/>
-      <c r="V6" s="17"/>
-      <c r="W6" s="18"/>
+      <c r="S6" s="10"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+      <c r="V6" s="10"/>
+      <c r="W6" s="11"/>
     </row>
     <row r="7" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1"/>
@@ -936,20 +936,20 @@
       <c r="W9" s="12"/>
     </row>
     <row r="11" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="15"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="8"/>
       <c r="F11" s="5"/>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="18"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="11"/>
     </row>
     <row r="12" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C12" s="3"/>
@@ -1080,20 +1080,20 @@
       <c r="L24" s="12"/>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="14"/>
-      <c r="E26" s="15"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="8"/>
       <c r="F26" s="5"/>
-      <c r="G26" s="16" t="s">
+      <c r="G26" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="18"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="11"/>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C27" s="3"/>
@@ -1109,7 +1109,7 @@
       <c r="K27" s="12"/>
       <c r="L27" s="12"/>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -1130,20 +1130,20 @@
       <c r="L29" s="12"/>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="14"/>
-      <c r="E31" s="15"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="8"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="16" t="s">
+      <c r="G31" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="18"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="11"/>
     </row>
     <row r="32" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C32" s="3"/>
@@ -1164,7 +1164,9 @@
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="12"/>
+      <c r="G33" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
       <c r="J33" s="12"/>
@@ -1180,20 +1182,20 @@
       <c r="L34" s="12"/>
     </row>
     <row r="36" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D36" s="14"/>
-      <c r="E36" s="15"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="8"/>
       <c r="F36" s="5"/>
-      <c r="G36" s="16" t="s">
+      <c r="G36" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="18"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="11"/>
     </row>
     <row r="37" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C37" s="3"/>
@@ -1228,20 +1230,20 @@
       <c r="L39" s="12"/>
     </row>
     <row r="41" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="14"/>
-      <c r="E41" s="15"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="8"/>
       <c r="F41" s="5"/>
-      <c r="G41" s="16" t="s">
+      <c r="G41" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="18"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="11"/>
     </row>
     <row r="42" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C42" s="3"/>
@@ -1276,20 +1278,20 @@
       <c r="L44" s="12"/>
     </row>
     <row r="46" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="14"/>
-      <c r="E46" s="15"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="8"/>
       <c r="F46" s="5"/>
-      <c r="G46" s="16" t="s">
+      <c r="G46" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H46" s="17"/>
-      <c r="I46" s="17"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="17"/>
-      <c r="L46" s="18"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="11"/>
     </row>
     <row r="47" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C47" s="3"/>
@@ -1324,20 +1326,20 @@
       <c r="L49" s="12"/>
     </row>
     <row r="51" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C51" s="13" t="s">
+      <c r="C51" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="15"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="8"/>
       <c r="F51" s="5"/>
-      <c r="G51" s="16" t="s">
+      <c r="G51" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H51" s="17"/>
-      <c r="I51" s="17"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="18"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="11"/>
     </row>
     <row r="52" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C52" s="3"/>
@@ -1372,20 +1374,20 @@
       <c r="L54" s="12"/>
     </row>
     <row r="56" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C56" s="13" t="s">
+      <c r="C56" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D56" s="14"/>
-      <c r="E56" s="15"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="8"/>
       <c r="F56" s="5"/>
-      <c r="G56" s="16" t="s">
+      <c r="G56" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H56" s="17"/>
-      <c r="I56" s="17"/>
-      <c r="J56" s="17"/>
-      <c r="K56" s="17"/>
-      <c r="L56" s="18"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
+      <c r="K56" s="10"/>
+      <c r="L56" s="11"/>
     </row>
     <row r="57" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C57" s="3"/>
@@ -1420,20 +1422,20 @@
       <c r="L59" s="12"/>
     </row>
     <row r="61" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C61" s="13" t="s">
+      <c r="C61" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D61" s="14"/>
-      <c r="E61" s="15"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="8"/>
       <c r="F61" s="5"/>
-      <c r="G61" s="16" t="s">
+      <c r="G61" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H61" s="17"/>
-      <c r="I61" s="17"/>
-      <c r="J61" s="17"/>
-      <c r="K61" s="17"/>
-      <c r="L61" s="18"/>
+      <c r="H61" s="10"/>
+      <c r="I61" s="10"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="10"/>
+      <c r="L61" s="11"/>
     </row>
     <row r="62" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C62" s="3"/>
@@ -1468,20 +1470,20 @@
       <c r="L64" s="12"/>
     </row>
     <row r="66" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C66" s="13" t="s">
+      <c r="C66" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D66" s="14"/>
-      <c r="E66" s="15"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="8"/>
       <c r="F66" s="5"/>
-      <c r="G66" s="16" t="s">
+      <c r="G66" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H66" s="17"/>
-      <c r="I66" s="17"/>
-      <c r="J66" s="17"/>
-      <c r="K66" s="17"/>
-      <c r="L66" s="18"/>
+      <c r="H66" s="10"/>
+      <c r="I66" s="10"/>
+      <c r="J66" s="10"/>
+      <c r="K66" s="10"/>
+      <c r="L66" s="11"/>
     </row>
     <row r="67" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C67" s="3"/>
@@ -1516,20 +1518,20 @@
       <c r="L69" s="12"/>
     </row>
     <row r="71" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C71" s="13" t="s">
+      <c r="C71" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D71" s="14"/>
-      <c r="E71" s="15"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="8"/>
       <c r="F71" s="5"/>
-      <c r="G71" s="16" t="s">
+      <c r="G71" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H71" s="17"/>
-      <c r="I71" s="17"/>
-      <c r="J71" s="17"/>
-      <c r="K71" s="17"/>
-      <c r="L71" s="18"/>
+      <c r="H71" s="10"/>
+      <c r="I71" s="10"/>
+      <c r="J71" s="10"/>
+      <c r="K71" s="10"/>
+      <c r="L71" s="11"/>
     </row>
     <row r="72" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C72" s="3"/>
@@ -1566,20 +1568,20 @@
       <c r="L74" s="12"/>
     </row>
     <row r="76" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C76" s="13" t="s">
+      <c r="C76" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D76" s="14"/>
-      <c r="E76" s="15"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="8"/>
       <c r="F76" s="5"/>
-      <c r="G76" s="16" t="s">
+      <c r="G76" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H76" s="17"/>
-      <c r="I76" s="17"/>
-      <c r="J76" s="17"/>
-      <c r="K76" s="17"/>
-      <c r="L76" s="18"/>
+      <c r="H76" s="10"/>
+      <c r="I76" s="10"/>
+      <c r="J76" s="10"/>
+      <c r="K76" s="10"/>
+      <c r="L76" s="11"/>
     </row>
     <row r="77" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C77" s="3"/>
@@ -1616,20 +1618,20 @@
       <c r="L79" s="12"/>
     </row>
     <row r="81" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C81" s="13" t="s">
+      <c r="C81" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D81" s="14"/>
-      <c r="E81" s="15"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="8"/>
       <c r="F81" s="5"/>
-      <c r="G81" s="16" t="s">
+      <c r="G81" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H81" s="17"/>
-      <c r="I81" s="17"/>
-      <c r="J81" s="17"/>
-      <c r="K81" s="17"/>
-      <c r="L81" s="18"/>
+      <c r="H81" s="10"/>
+      <c r="I81" s="10"/>
+      <c r="J81" s="10"/>
+      <c r="K81" s="10"/>
+      <c r="L81" s="11"/>
     </row>
     <row r="82" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C82" s="3"/>
@@ -1664,20 +1666,20 @@
       <c r="L84" s="12"/>
     </row>
     <row r="86" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C86" s="13" t="s">
+      <c r="C86" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D86" s="14"/>
-      <c r="E86" s="15"/>
+      <c r="D86" s="7"/>
+      <c r="E86" s="8"/>
       <c r="F86" s="5"/>
-      <c r="G86" s="16" t="s">
+      <c r="G86" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H86" s="17"/>
-      <c r="I86" s="17"/>
-      <c r="J86" s="17"/>
-      <c r="K86" s="17"/>
-      <c r="L86" s="18"/>
+      <c r="H86" s="10"/>
+      <c r="I86" s="10"/>
+      <c r="J86" s="10"/>
+      <c r="K86" s="10"/>
+      <c r="L86" s="11"/>
     </row>
     <row r="87" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C87" s="3"/>
@@ -1714,20 +1716,20 @@
       <c r="L89" s="12"/>
     </row>
     <row r="91" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C91" s="13" t="s">
+      <c r="C91" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D91" s="14"/>
-      <c r="E91" s="15"/>
+      <c r="D91" s="7"/>
+      <c r="E91" s="8"/>
       <c r="F91" s="5"/>
-      <c r="G91" s="16" t="s">
+      <c r="G91" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H91" s="17"/>
-      <c r="I91" s="17"/>
-      <c r="J91" s="17"/>
-      <c r="K91" s="17"/>
-      <c r="L91" s="18"/>
+      <c r="H91" s="10"/>
+      <c r="I91" s="10"/>
+      <c r="J91" s="10"/>
+      <c r="K91" s="10"/>
+      <c r="L91" s="11"/>
     </row>
     <row r="92" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C92" s="3"/>
@@ -1762,20 +1764,20 @@
       <c r="L94" s="12"/>
     </row>
     <row r="96" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C96" s="13" t="s">
+      <c r="C96" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D96" s="14"/>
-      <c r="E96" s="15"/>
+      <c r="D96" s="7"/>
+      <c r="E96" s="8"/>
       <c r="F96" s="5"/>
-      <c r="G96" s="16" t="s">
+      <c r="G96" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H96" s="17"/>
-      <c r="I96" s="17"/>
-      <c r="J96" s="17"/>
-      <c r="K96" s="17"/>
-      <c r="L96" s="18"/>
+      <c r="H96" s="10"/>
+      <c r="I96" s="10"/>
+      <c r="J96" s="10"/>
+      <c r="K96" s="10"/>
+      <c r="L96" s="11"/>
     </row>
     <row r="97" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C97" s="3"/>
@@ -1811,6 +1813,83 @@
     </row>
   </sheetData>
   <mergeCells count="101">
+    <mergeCell ref="G2:Q3"/>
+    <mergeCell ref="G99:L99"/>
+    <mergeCell ref="C96:E96"/>
+    <mergeCell ref="G96:L96"/>
+    <mergeCell ref="G97:L97"/>
+    <mergeCell ref="G98:L98"/>
+    <mergeCell ref="G9:L9"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="G12:L12"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="G7:L7"/>
+    <mergeCell ref="G8:L8"/>
+    <mergeCell ref="G13:L13"/>
+    <mergeCell ref="G14:L14"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="G16:L16"/>
+    <mergeCell ref="G17:L17"/>
+    <mergeCell ref="G18:L18"/>
+    <mergeCell ref="G19:L19"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="G21:L21"/>
+    <mergeCell ref="G22:L22"/>
+    <mergeCell ref="G23:L23"/>
+    <mergeCell ref="G24:L24"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="G26:L26"/>
+    <mergeCell ref="G27:L27"/>
+    <mergeCell ref="G28:L28"/>
+    <mergeCell ref="G29:L29"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="G31:L31"/>
+    <mergeCell ref="G32:L32"/>
+    <mergeCell ref="G33:L33"/>
+    <mergeCell ref="G34:L34"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="G36:L36"/>
+    <mergeCell ref="G37:L37"/>
+    <mergeCell ref="G38:L38"/>
+    <mergeCell ref="G39:L39"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="G41:L41"/>
+    <mergeCell ref="G56:L56"/>
+    <mergeCell ref="G57:L57"/>
+    <mergeCell ref="G58:L58"/>
+    <mergeCell ref="G59:L59"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="G61:L61"/>
+    <mergeCell ref="G42:L42"/>
+    <mergeCell ref="G43:L43"/>
+    <mergeCell ref="G44:L44"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="G46:L46"/>
+    <mergeCell ref="G47:L47"/>
+    <mergeCell ref="G48:L48"/>
+    <mergeCell ref="G49:L49"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="G51:L51"/>
+    <mergeCell ref="G87:L87"/>
+    <mergeCell ref="G93:L93"/>
+    <mergeCell ref="G94:L94"/>
+    <mergeCell ref="G88:L88"/>
+    <mergeCell ref="G89:L89"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="G91:L91"/>
+    <mergeCell ref="G92:L92"/>
+    <mergeCell ref="G72:L72"/>
+    <mergeCell ref="G73:L73"/>
+    <mergeCell ref="G74:L74"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="G76:L76"/>
+    <mergeCell ref="G77:L77"/>
+    <mergeCell ref="G78:L78"/>
+    <mergeCell ref="G79:L79"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="G81:L81"/>
     <mergeCell ref="N6:P6"/>
     <mergeCell ref="R6:W6"/>
     <mergeCell ref="R7:W7"/>
@@ -1835,83 +1914,6 @@
     <mergeCell ref="G53:L53"/>
     <mergeCell ref="G54:L54"/>
     <mergeCell ref="C56:E56"/>
-    <mergeCell ref="G87:L87"/>
-    <mergeCell ref="G93:L93"/>
-    <mergeCell ref="G94:L94"/>
-    <mergeCell ref="G88:L88"/>
-    <mergeCell ref="G89:L89"/>
-    <mergeCell ref="C91:E91"/>
-    <mergeCell ref="G91:L91"/>
-    <mergeCell ref="G92:L92"/>
-    <mergeCell ref="G72:L72"/>
-    <mergeCell ref="G73:L73"/>
-    <mergeCell ref="G74:L74"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="G76:L76"/>
-    <mergeCell ref="G77:L77"/>
-    <mergeCell ref="G78:L78"/>
-    <mergeCell ref="G79:L79"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="G81:L81"/>
-    <mergeCell ref="G56:L56"/>
-    <mergeCell ref="G57:L57"/>
-    <mergeCell ref="G58:L58"/>
-    <mergeCell ref="G59:L59"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="G61:L61"/>
-    <mergeCell ref="G42:L42"/>
-    <mergeCell ref="G43:L43"/>
-    <mergeCell ref="G44:L44"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="G46:L46"/>
-    <mergeCell ref="G47:L47"/>
-    <mergeCell ref="G48:L48"/>
-    <mergeCell ref="G49:L49"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="G51:L51"/>
-    <mergeCell ref="G32:L32"/>
-    <mergeCell ref="G33:L33"/>
-    <mergeCell ref="G34:L34"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="G36:L36"/>
-    <mergeCell ref="G37:L37"/>
-    <mergeCell ref="G38:L38"/>
-    <mergeCell ref="G39:L39"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="G41:L41"/>
-    <mergeCell ref="G23:L23"/>
-    <mergeCell ref="G24:L24"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="G26:L26"/>
-    <mergeCell ref="G27:L27"/>
-    <mergeCell ref="G28:L28"/>
-    <mergeCell ref="G29:L29"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="G31:L31"/>
-    <mergeCell ref="G2:Q3"/>
-    <mergeCell ref="G99:L99"/>
-    <mergeCell ref="C96:E96"/>
-    <mergeCell ref="G96:L96"/>
-    <mergeCell ref="G97:L97"/>
-    <mergeCell ref="G98:L98"/>
-    <mergeCell ref="G9:L9"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="G12:L12"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="G6:L6"/>
-    <mergeCell ref="G7:L7"/>
-    <mergeCell ref="G8:L8"/>
-    <mergeCell ref="G13:L13"/>
-    <mergeCell ref="G14:L14"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="G16:L16"/>
-    <mergeCell ref="G17:L17"/>
-    <mergeCell ref="G18:L18"/>
-    <mergeCell ref="G19:L19"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="G21:L21"/>
-    <mergeCell ref="G22:L22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data_Structures_and_Algorithms.xlsx
+++ b/Data_Structures_and_Algorithms.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nvjsi\Desktop\My Projects\pro-data-structures-and-algorithms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2957CD65-CFD6-4B95-BB61-F2F8D64EEC90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5362442-85E9-4509-8195-2F14357E7AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{463DEBCD-443E-4114-A884-3BF4F43F1855}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="29">
   <si>
     <t>Data Structures and Algorithms</t>
   </si>
@@ -109,6 +109,9 @@
   </si>
   <si>
     <t>merge interval</t>
+  </si>
+  <si>
+    <t>kadane's algorithm</t>
   </si>
 </sst>
 </file>
@@ -388,6 +391,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -404,27 +428,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -795,32 +798,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="15"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="8"/>
     </row>
     <row r="3" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G3" s="16"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="18"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="11"/>
     </row>
     <row r="5" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2"/>
@@ -841,35 +844,35 @@
     </row>
     <row r="6" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="1"/>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="15"/>
       <c r="F6" s="5"/>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="11"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="18"/>
       <c r="M6" s="1"/>
-      <c r="N6" s="6" t="s">
+      <c r="N6" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="O6" s="7"/>
-      <c r="P6" s="8"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="15"/>
       <c r="Q6" s="5"/>
-      <c r="R6" s="9" t="s">
+      <c r="R6" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="S6" s="10"/>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10"/>
-      <c r="V6" s="10"/>
-      <c r="W6" s="11"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="18"/>
     </row>
     <row r="7" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1"/>
@@ -936,20 +939,20 @@
       <c r="W9" s="12"/>
     </row>
     <row r="11" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="8"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="15"/>
       <c r="F11" s="5"/>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="11"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="18"/>
     </row>
     <row r="12" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C12" s="3"/>
@@ -1080,20 +1083,20 @@
       <c r="L24" s="12"/>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="7"/>
-      <c r="E26" s="8"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="15"/>
       <c r="F26" s="5"/>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="11"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="18"/>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C27" s="3"/>
@@ -1114,7 +1117,9 @@
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
-      <c r="G28" s="12"/>
+      <c r="G28" s="12" t="s">
+        <v>28</v>
+      </c>
       <c r="H28" s="12"/>
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
@@ -1130,20 +1135,20 @@
       <c r="L29" s="12"/>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="7"/>
-      <c r="E31" s="8"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="15"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="9" t="s">
+      <c r="G31" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="11"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="18"/>
     </row>
     <row r="32" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C32" s="3"/>
@@ -1182,20 +1187,20 @@
       <c r="L34" s="12"/>
     </row>
     <row r="36" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D36" s="7"/>
-      <c r="E36" s="8"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="15"/>
       <c r="F36" s="5"/>
-      <c r="G36" s="9" t="s">
+      <c r="G36" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="11"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="18"/>
     </row>
     <row r="37" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C37" s="3"/>
@@ -1230,20 +1235,20 @@
       <c r="L39" s="12"/>
     </row>
     <row r="41" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="7"/>
-      <c r="E41" s="8"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="15"/>
       <c r="F41" s="5"/>
-      <c r="G41" s="9" t="s">
+      <c r="G41" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="11"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="18"/>
     </row>
     <row r="42" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C42" s="3"/>
@@ -1278,20 +1283,20 @@
       <c r="L44" s="12"/>
     </row>
     <row r="46" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="7"/>
-      <c r="E46" s="8"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="15"/>
       <c r="F46" s="5"/>
-      <c r="G46" s="9" t="s">
+      <c r="G46" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="11"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="18"/>
     </row>
     <row r="47" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C47" s="3"/>
@@ -1326,20 +1331,20 @@
       <c r="L49" s="12"/>
     </row>
     <row r="51" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="7"/>
-      <c r="E51" s="8"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="15"/>
       <c r="F51" s="5"/>
-      <c r="G51" s="9" t="s">
+      <c r="G51" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="11"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="17"/>
+      <c r="J51" s="17"/>
+      <c r="K51" s="17"/>
+      <c r="L51" s="18"/>
     </row>
     <row r="52" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C52" s="3"/>
@@ -1374,20 +1379,20 @@
       <c r="L54" s="12"/>
     </row>
     <row r="56" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D56" s="7"/>
-      <c r="E56" s="8"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="15"/>
       <c r="F56" s="5"/>
-      <c r="G56" s="9" t="s">
+      <c r="G56" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H56" s="10"/>
-      <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
-      <c r="K56" s="10"/>
-      <c r="L56" s="11"/>
+      <c r="H56" s="17"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="17"/>
+      <c r="K56" s="17"/>
+      <c r="L56" s="18"/>
     </row>
     <row r="57" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C57" s="3"/>
@@ -1422,20 +1427,20 @@
       <c r="L59" s="12"/>
     </row>
     <row r="61" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D61" s="7"/>
-      <c r="E61" s="8"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="15"/>
       <c r="F61" s="5"/>
-      <c r="G61" s="9" t="s">
+      <c r="G61" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H61" s="10"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
-      <c r="K61" s="10"/>
-      <c r="L61" s="11"/>
+      <c r="H61" s="17"/>
+      <c r="I61" s="17"/>
+      <c r="J61" s="17"/>
+      <c r="K61" s="17"/>
+      <c r="L61" s="18"/>
     </row>
     <row r="62" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C62" s="3"/>
@@ -1470,20 +1475,20 @@
       <c r="L64" s="12"/>
     </row>
     <row r="66" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D66" s="7"/>
-      <c r="E66" s="8"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="15"/>
       <c r="F66" s="5"/>
-      <c r="G66" s="9" t="s">
+      <c r="G66" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H66" s="10"/>
-      <c r="I66" s="10"/>
-      <c r="J66" s="10"/>
-      <c r="K66" s="10"/>
-      <c r="L66" s="11"/>
+      <c r="H66" s="17"/>
+      <c r="I66" s="17"/>
+      <c r="J66" s="17"/>
+      <c r="K66" s="17"/>
+      <c r="L66" s="18"/>
     </row>
     <row r="67" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C67" s="3"/>
@@ -1518,20 +1523,20 @@
       <c r="L69" s="12"/>
     </row>
     <row r="71" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C71" s="6" t="s">
+      <c r="C71" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D71" s="7"/>
-      <c r="E71" s="8"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="15"/>
       <c r="F71" s="5"/>
-      <c r="G71" s="9" t="s">
+      <c r="G71" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H71" s="10"/>
-      <c r="I71" s="10"/>
-      <c r="J71" s="10"/>
-      <c r="K71" s="10"/>
-      <c r="L71" s="11"/>
+      <c r="H71" s="17"/>
+      <c r="I71" s="17"/>
+      <c r="J71" s="17"/>
+      <c r="K71" s="17"/>
+      <c r="L71" s="18"/>
     </row>
     <row r="72" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C72" s="3"/>
@@ -1568,20 +1573,20 @@
       <c r="L74" s="12"/>
     </row>
     <row r="76" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C76" s="6" t="s">
+      <c r="C76" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D76" s="7"/>
-      <c r="E76" s="8"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="15"/>
       <c r="F76" s="5"/>
-      <c r="G76" s="9" t="s">
+      <c r="G76" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H76" s="10"/>
-      <c r="I76" s="10"/>
-      <c r="J76" s="10"/>
-      <c r="K76" s="10"/>
-      <c r="L76" s="11"/>
+      <c r="H76" s="17"/>
+      <c r="I76" s="17"/>
+      <c r="J76" s="17"/>
+      <c r="K76" s="17"/>
+      <c r="L76" s="18"/>
     </row>
     <row r="77" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C77" s="3"/>
@@ -1618,20 +1623,20 @@
       <c r="L79" s="12"/>
     </row>
     <row r="81" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C81" s="6" t="s">
+      <c r="C81" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D81" s="7"/>
-      <c r="E81" s="8"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="15"/>
       <c r="F81" s="5"/>
-      <c r="G81" s="9" t="s">
+      <c r="G81" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H81" s="10"/>
-      <c r="I81" s="10"/>
-      <c r="J81" s="10"/>
-      <c r="K81" s="10"/>
-      <c r="L81" s="11"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="17"/>
+      <c r="K81" s="17"/>
+      <c r="L81" s="18"/>
     </row>
     <row r="82" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C82" s="3"/>
@@ -1666,20 +1671,20 @@
       <c r="L84" s="12"/>
     </row>
     <row r="86" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C86" s="6" t="s">
+      <c r="C86" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D86" s="7"/>
-      <c r="E86" s="8"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="15"/>
       <c r="F86" s="5"/>
-      <c r="G86" s="9" t="s">
+      <c r="G86" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H86" s="10"/>
-      <c r="I86" s="10"/>
-      <c r="J86" s="10"/>
-      <c r="K86" s="10"/>
-      <c r="L86" s="11"/>
+      <c r="H86" s="17"/>
+      <c r="I86" s="17"/>
+      <c r="J86" s="17"/>
+      <c r="K86" s="17"/>
+      <c r="L86" s="18"/>
     </row>
     <row r="87" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C87" s="3"/>
@@ -1716,20 +1721,20 @@
       <c r="L89" s="12"/>
     </row>
     <row r="91" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C91" s="6" t="s">
+      <c r="C91" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D91" s="7"/>
-      <c r="E91" s="8"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="15"/>
       <c r="F91" s="5"/>
-      <c r="G91" s="9" t="s">
+      <c r="G91" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H91" s="10"/>
-      <c r="I91" s="10"/>
-      <c r="J91" s="10"/>
-      <c r="K91" s="10"/>
-      <c r="L91" s="11"/>
+      <c r="H91" s="17"/>
+      <c r="I91" s="17"/>
+      <c r="J91" s="17"/>
+      <c r="K91" s="17"/>
+      <c r="L91" s="18"/>
     </row>
     <row r="92" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C92" s="3"/>
@@ -1764,20 +1769,20 @@
       <c r="L94" s="12"/>
     </row>
     <row r="96" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C96" s="6" t="s">
+      <c r="C96" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D96" s="7"/>
-      <c r="E96" s="8"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="15"/>
       <c r="F96" s="5"/>
-      <c r="G96" s="9" t="s">
+      <c r="G96" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H96" s="10"/>
-      <c r="I96" s="10"/>
-      <c r="J96" s="10"/>
-      <c r="K96" s="10"/>
-      <c r="L96" s="11"/>
+      <c r="H96" s="17"/>
+      <c r="I96" s="17"/>
+      <c r="J96" s="17"/>
+      <c r="K96" s="17"/>
+      <c r="L96" s="18"/>
     </row>
     <row r="97" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C97" s="3"/>
@@ -1813,6 +1818,83 @@
     </row>
   </sheetData>
   <mergeCells count="101">
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:W6"/>
+    <mergeCell ref="R7:W7"/>
+    <mergeCell ref="R8:W8"/>
+    <mergeCell ref="R9:W9"/>
+    <mergeCell ref="G82:L82"/>
+    <mergeCell ref="G83:L83"/>
+    <mergeCell ref="G84:L84"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="G86:L86"/>
+    <mergeCell ref="G62:L62"/>
+    <mergeCell ref="G63:L63"/>
+    <mergeCell ref="G64:L64"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="G66:L66"/>
+    <mergeCell ref="G67:L67"/>
+    <mergeCell ref="G68:L68"/>
+    <mergeCell ref="G69:L69"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="G71:L71"/>
+    <mergeCell ref="G52:L52"/>
+    <mergeCell ref="G53:L53"/>
+    <mergeCell ref="G54:L54"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="G87:L87"/>
+    <mergeCell ref="G93:L93"/>
+    <mergeCell ref="G94:L94"/>
+    <mergeCell ref="G88:L88"/>
+    <mergeCell ref="G89:L89"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="G91:L91"/>
+    <mergeCell ref="G92:L92"/>
+    <mergeCell ref="G72:L72"/>
+    <mergeCell ref="G73:L73"/>
+    <mergeCell ref="G74:L74"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="G76:L76"/>
+    <mergeCell ref="G77:L77"/>
+    <mergeCell ref="G78:L78"/>
+    <mergeCell ref="G79:L79"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="G81:L81"/>
+    <mergeCell ref="G56:L56"/>
+    <mergeCell ref="G57:L57"/>
+    <mergeCell ref="G58:L58"/>
+    <mergeCell ref="G59:L59"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="G61:L61"/>
+    <mergeCell ref="G42:L42"/>
+    <mergeCell ref="G43:L43"/>
+    <mergeCell ref="G44:L44"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="G46:L46"/>
+    <mergeCell ref="G47:L47"/>
+    <mergeCell ref="G48:L48"/>
+    <mergeCell ref="G49:L49"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="G51:L51"/>
+    <mergeCell ref="G32:L32"/>
+    <mergeCell ref="G33:L33"/>
+    <mergeCell ref="G34:L34"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="G36:L36"/>
+    <mergeCell ref="G37:L37"/>
+    <mergeCell ref="G38:L38"/>
+    <mergeCell ref="G39:L39"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="G41:L41"/>
+    <mergeCell ref="G23:L23"/>
+    <mergeCell ref="G24:L24"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="G26:L26"/>
+    <mergeCell ref="G27:L27"/>
+    <mergeCell ref="G28:L28"/>
+    <mergeCell ref="G29:L29"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="G31:L31"/>
     <mergeCell ref="G2:Q3"/>
     <mergeCell ref="G99:L99"/>
     <mergeCell ref="C96:E96"/>
@@ -1837,83 +1919,6 @@
     <mergeCell ref="C21:E21"/>
     <mergeCell ref="G21:L21"/>
     <mergeCell ref="G22:L22"/>
-    <mergeCell ref="G23:L23"/>
-    <mergeCell ref="G24:L24"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="G26:L26"/>
-    <mergeCell ref="G27:L27"/>
-    <mergeCell ref="G28:L28"/>
-    <mergeCell ref="G29:L29"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="G31:L31"/>
-    <mergeCell ref="G32:L32"/>
-    <mergeCell ref="G33:L33"/>
-    <mergeCell ref="G34:L34"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="G36:L36"/>
-    <mergeCell ref="G37:L37"/>
-    <mergeCell ref="G38:L38"/>
-    <mergeCell ref="G39:L39"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="G41:L41"/>
-    <mergeCell ref="G56:L56"/>
-    <mergeCell ref="G57:L57"/>
-    <mergeCell ref="G58:L58"/>
-    <mergeCell ref="G59:L59"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="G61:L61"/>
-    <mergeCell ref="G42:L42"/>
-    <mergeCell ref="G43:L43"/>
-    <mergeCell ref="G44:L44"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="G46:L46"/>
-    <mergeCell ref="G47:L47"/>
-    <mergeCell ref="G48:L48"/>
-    <mergeCell ref="G49:L49"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="G51:L51"/>
-    <mergeCell ref="G87:L87"/>
-    <mergeCell ref="G93:L93"/>
-    <mergeCell ref="G94:L94"/>
-    <mergeCell ref="G88:L88"/>
-    <mergeCell ref="G89:L89"/>
-    <mergeCell ref="C91:E91"/>
-    <mergeCell ref="G91:L91"/>
-    <mergeCell ref="G92:L92"/>
-    <mergeCell ref="G72:L72"/>
-    <mergeCell ref="G73:L73"/>
-    <mergeCell ref="G74:L74"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="G76:L76"/>
-    <mergeCell ref="G77:L77"/>
-    <mergeCell ref="G78:L78"/>
-    <mergeCell ref="G79:L79"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="G81:L81"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:W6"/>
-    <mergeCell ref="R7:W7"/>
-    <mergeCell ref="R8:W8"/>
-    <mergeCell ref="R9:W9"/>
-    <mergeCell ref="G82:L82"/>
-    <mergeCell ref="G83:L83"/>
-    <mergeCell ref="G84:L84"/>
-    <mergeCell ref="C86:E86"/>
-    <mergeCell ref="G86:L86"/>
-    <mergeCell ref="G62:L62"/>
-    <mergeCell ref="G63:L63"/>
-    <mergeCell ref="G64:L64"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="G66:L66"/>
-    <mergeCell ref="G67:L67"/>
-    <mergeCell ref="G68:L68"/>
-    <mergeCell ref="G69:L69"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="G71:L71"/>
-    <mergeCell ref="G52:L52"/>
-    <mergeCell ref="G53:L53"/>
-    <mergeCell ref="G54:L54"/>
-    <mergeCell ref="C56:E56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data_Structures_and_Algorithms.xlsx
+++ b/Data_Structures_and_Algorithms.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nvjsi\Desktop\My Projects\pro-data-structures-and-algorithms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5362442-85E9-4509-8195-2F14357E7AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D5C8E6-3A36-47D4-8AB6-3DFD5A9C39CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{463DEBCD-443E-4114-A884-3BF4F43F1855}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="30">
   <si>
     <t>Data Structures and Algorithms</t>
   </si>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t>kadane's algorithm</t>
+  </si>
+  <si>
+    <t>prefix and suffix sum</t>
   </si>
 </sst>
 </file>
@@ -391,6 +394,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -407,27 +431,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -798,32 +801,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="8"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="15"/>
     </row>
     <row r="3" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G3" s="9"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="11"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="18"/>
     </row>
     <row r="5" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2"/>
@@ -844,35 +847,35 @@
     </row>
     <row r="6" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="1"/>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="15"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="8"/>
       <c r="F6" s="5"/>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="18"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="11"/>
       <c r="M6" s="1"/>
-      <c r="N6" s="13" t="s">
+      <c r="N6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="O6" s="14"/>
-      <c r="P6" s="15"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="8"/>
       <c r="Q6" s="5"/>
-      <c r="R6" s="16" t="s">
+      <c r="R6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="S6" s="17"/>
-      <c r="T6" s="17"/>
-      <c r="U6" s="17"/>
-      <c r="V6" s="17"/>
-      <c r="W6" s="18"/>
+      <c r="S6" s="10"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+      <c r="V6" s="10"/>
+      <c r="W6" s="11"/>
     </row>
     <row r="7" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1"/>
@@ -906,7 +909,9 @@
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="12"/>
+      <c r="G8" s="12" t="s">
+        <v>29</v>
+      </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
@@ -939,20 +944,20 @@
       <c r="W9" s="12"/>
     </row>
     <row r="11" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="15"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="8"/>
       <c r="F11" s="5"/>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="18"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="11"/>
     </row>
     <row r="12" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C12" s="3"/>
@@ -1083,20 +1088,20 @@
       <c r="L24" s="12"/>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="14"/>
-      <c r="E26" s="15"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="8"/>
       <c r="F26" s="5"/>
-      <c r="G26" s="16" t="s">
+      <c r="G26" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="18"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="11"/>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C27" s="3"/>
@@ -1135,20 +1140,20 @@
       <c r="L29" s="12"/>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="14"/>
-      <c r="E31" s="15"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="8"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="16" t="s">
+      <c r="G31" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="18"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="11"/>
     </row>
     <row r="32" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C32" s="3"/>
@@ -1187,20 +1192,20 @@
       <c r="L34" s="12"/>
     </row>
     <row r="36" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D36" s="14"/>
-      <c r="E36" s="15"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="8"/>
       <c r="F36" s="5"/>
-      <c r="G36" s="16" t="s">
+      <c r="G36" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="18"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="11"/>
     </row>
     <row r="37" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C37" s="3"/>
@@ -1235,20 +1240,20 @@
       <c r="L39" s="12"/>
     </row>
     <row r="41" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="14"/>
-      <c r="E41" s="15"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="8"/>
       <c r="F41" s="5"/>
-      <c r="G41" s="16" t="s">
+      <c r="G41" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="18"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="11"/>
     </row>
     <row r="42" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C42" s="3"/>
@@ -1283,20 +1288,20 @@
       <c r="L44" s="12"/>
     </row>
     <row r="46" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="14"/>
-      <c r="E46" s="15"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="8"/>
       <c r="F46" s="5"/>
-      <c r="G46" s="16" t="s">
+      <c r="G46" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H46" s="17"/>
-      <c r="I46" s="17"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="17"/>
-      <c r="L46" s="18"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="11"/>
     </row>
     <row r="47" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C47" s="3"/>
@@ -1331,20 +1336,20 @@
       <c r="L49" s="12"/>
     </row>
     <row r="51" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C51" s="13" t="s">
+      <c r="C51" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="15"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="8"/>
       <c r="F51" s="5"/>
-      <c r="G51" s="16" t="s">
+      <c r="G51" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H51" s="17"/>
-      <c r="I51" s="17"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="18"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="11"/>
     </row>
     <row r="52" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C52" s="3"/>
@@ -1379,20 +1384,20 @@
       <c r="L54" s="12"/>
     </row>
     <row r="56" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C56" s="13" t="s">
+      <c r="C56" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D56" s="14"/>
-      <c r="E56" s="15"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="8"/>
       <c r="F56" s="5"/>
-      <c r="G56" s="16" t="s">
+      <c r="G56" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H56" s="17"/>
-      <c r="I56" s="17"/>
-      <c r="J56" s="17"/>
-      <c r="K56" s="17"/>
-      <c r="L56" s="18"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
+      <c r="K56" s="10"/>
+      <c r="L56" s="11"/>
     </row>
     <row r="57" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C57" s="3"/>
@@ -1427,20 +1432,20 @@
       <c r="L59" s="12"/>
     </row>
     <row r="61" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C61" s="13" t="s">
+      <c r="C61" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D61" s="14"/>
-      <c r="E61" s="15"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="8"/>
       <c r="F61" s="5"/>
-      <c r="G61" s="16" t="s">
+      <c r="G61" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H61" s="17"/>
-      <c r="I61" s="17"/>
-      <c r="J61" s="17"/>
-      <c r="K61" s="17"/>
-      <c r="L61" s="18"/>
+      <c r="H61" s="10"/>
+      <c r="I61" s="10"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="10"/>
+      <c r="L61" s="11"/>
     </row>
     <row r="62" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C62" s="3"/>
@@ -1475,20 +1480,20 @@
       <c r="L64" s="12"/>
     </row>
     <row r="66" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C66" s="13" t="s">
+      <c r="C66" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D66" s="14"/>
-      <c r="E66" s="15"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="8"/>
       <c r="F66" s="5"/>
-      <c r="G66" s="16" t="s">
+      <c r="G66" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H66" s="17"/>
-      <c r="I66" s="17"/>
-      <c r="J66" s="17"/>
-      <c r="K66" s="17"/>
-      <c r="L66" s="18"/>
+      <c r="H66" s="10"/>
+      <c r="I66" s="10"/>
+      <c r="J66" s="10"/>
+      <c r="K66" s="10"/>
+      <c r="L66" s="11"/>
     </row>
     <row r="67" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C67" s="3"/>
@@ -1523,20 +1528,20 @@
       <c r="L69" s="12"/>
     </row>
     <row r="71" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C71" s="13" t="s">
+      <c r="C71" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D71" s="14"/>
-      <c r="E71" s="15"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="8"/>
       <c r="F71" s="5"/>
-      <c r="G71" s="16" t="s">
+      <c r="G71" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H71" s="17"/>
-      <c r="I71" s="17"/>
-      <c r="J71" s="17"/>
-      <c r="K71" s="17"/>
-      <c r="L71" s="18"/>
+      <c r="H71" s="10"/>
+      <c r="I71" s="10"/>
+      <c r="J71" s="10"/>
+      <c r="K71" s="10"/>
+      <c r="L71" s="11"/>
     </row>
     <row r="72" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C72" s="3"/>
@@ -1573,20 +1578,20 @@
       <c r="L74" s="12"/>
     </row>
     <row r="76" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C76" s="13" t="s">
+      <c r="C76" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D76" s="14"/>
-      <c r="E76" s="15"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="8"/>
       <c r="F76" s="5"/>
-      <c r="G76" s="16" t="s">
+      <c r="G76" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H76" s="17"/>
-      <c r="I76" s="17"/>
-      <c r="J76" s="17"/>
-      <c r="K76" s="17"/>
-      <c r="L76" s="18"/>
+      <c r="H76" s="10"/>
+      <c r="I76" s="10"/>
+      <c r="J76" s="10"/>
+      <c r="K76" s="10"/>
+      <c r="L76" s="11"/>
     </row>
     <row r="77" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C77" s="3"/>
@@ -1623,20 +1628,20 @@
       <c r="L79" s="12"/>
     </row>
     <row r="81" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C81" s="13" t="s">
+      <c r="C81" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D81" s="14"/>
-      <c r="E81" s="15"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="8"/>
       <c r="F81" s="5"/>
-      <c r="G81" s="16" t="s">
+      <c r="G81" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H81" s="17"/>
-      <c r="I81" s="17"/>
-      <c r="J81" s="17"/>
-      <c r="K81" s="17"/>
-      <c r="L81" s="18"/>
+      <c r="H81" s="10"/>
+      <c r="I81" s="10"/>
+      <c r="J81" s="10"/>
+      <c r="K81" s="10"/>
+      <c r="L81" s="11"/>
     </row>
     <row r="82" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C82" s="3"/>
@@ -1671,20 +1676,20 @@
       <c r="L84" s="12"/>
     </row>
     <row r="86" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C86" s="13" t="s">
+      <c r="C86" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D86" s="14"/>
-      <c r="E86" s="15"/>
+      <c r="D86" s="7"/>
+      <c r="E86" s="8"/>
       <c r="F86" s="5"/>
-      <c r="G86" s="16" t="s">
+      <c r="G86" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H86" s="17"/>
-      <c r="I86" s="17"/>
-      <c r="J86" s="17"/>
-      <c r="K86" s="17"/>
-      <c r="L86" s="18"/>
+      <c r="H86" s="10"/>
+      <c r="I86" s="10"/>
+      <c r="J86" s="10"/>
+      <c r="K86" s="10"/>
+      <c r="L86" s="11"/>
     </row>
     <row r="87" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C87" s="3"/>
@@ -1721,20 +1726,20 @@
       <c r="L89" s="12"/>
     </row>
     <row r="91" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C91" s="13" t="s">
+      <c r="C91" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D91" s="14"/>
-      <c r="E91" s="15"/>
+      <c r="D91" s="7"/>
+      <c r="E91" s="8"/>
       <c r="F91" s="5"/>
-      <c r="G91" s="16" t="s">
+      <c r="G91" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H91" s="17"/>
-      <c r="I91" s="17"/>
-      <c r="J91" s="17"/>
-      <c r="K91" s="17"/>
-      <c r="L91" s="18"/>
+      <c r="H91" s="10"/>
+      <c r="I91" s="10"/>
+      <c r="J91" s="10"/>
+      <c r="K91" s="10"/>
+      <c r="L91" s="11"/>
     </row>
     <row r="92" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C92" s="3"/>
@@ -1769,20 +1774,20 @@
       <c r="L94" s="12"/>
     </row>
     <row r="96" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C96" s="13" t="s">
+      <c r="C96" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D96" s="14"/>
-      <c r="E96" s="15"/>
+      <c r="D96" s="7"/>
+      <c r="E96" s="8"/>
       <c r="F96" s="5"/>
-      <c r="G96" s="16" t="s">
+      <c r="G96" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H96" s="17"/>
-      <c r="I96" s="17"/>
-      <c r="J96" s="17"/>
-      <c r="K96" s="17"/>
-      <c r="L96" s="18"/>
+      <c r="H96" s="10"/>
+      <c r="I96" s="10"/>
+      <c r="J96" s="10"/>
+      <c r="K96" s="10"/>
+      <c r="L96" s="11"/>
     </row>
     <row r="97" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C97" s="3"/>
@@ -1818,6 +1823,83 @@
     </row>
   </sheetData>
   <mergeCells count="101">
+    <mergeCell ref="G2:Q3"/>
+    <mergeCell ref="G99:L99"/>
+    <mergeCell ref="C96:E96"/>
+    <mergeCell ref="G96:L96"/>
+    <mergeCell ref="G97:L97"/>
+    <mergeCell ref="G98:L98"/>
+    <mergeCell ref="G9:L9"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="G12:L12"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="G7:L7"/>
+    <mergeCell ref="G8:L8"/>
+    <mergeCell ref="G13:L13"/>
+    <mergeCell ref="G14:L14"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="G16:L16"/>
+    <mergeCell ref="G17:L17"/>
+    <mergeCell ref="G18:L18"/>
+    <mergeCell ref="G19:L19"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="G21:L21"/>
+    <mergeCell ref="G22:L22"/>
+    <mergeCell ref="G23:L23"/>
+    <mergeCell ref="G24:L24"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="G26:L26"/>
+    <mergeCell ref="G27:L27"/>
+    <mergeCell ref="G28:L28"/>
+    <mergeCell ref="G29:L29"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="G31:L31"/>
+    <mergeCell ref="G32:L32"/>
+    <mergeCell ref="G33:L33"/>
+    <mergeCell ref="G34:L34"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="G36:L36"/>
+    <mergeCell ref="G37:L37"/>
+    <mergeCell ref="G38:L38"/>
+    <mergeCell ref="G39:L39"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="G41:L41"/>
+    <mergeCell ref="G56:L56"/>
+    <mergeCell ref="G57:L57"/>
+    <mergeCell ref="G58:L58"/>
+    <mergeCell ref="G59:L59"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="G61:L61"/>
+    <mergeCell ref="G42:L42"/>
+    <mergeCell ref="G43:L43"/>
+    <mergeCell ref="G44:L44"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="G46:L46"/>
+    <mergeCell ref="G47:L47"/>
+    <mergeCell ref="G48:L48"/>
+    <mergeCell ref="G49:L49"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="G51:L51"/>
+    <mergeCell ref="G87:L87"/>
+    <mergeCell ref="G93:L93"/>
+    <mergeCell ref="G94:L94"/>
+    <mergeCell ref="G88:L88"/>
+    <mergeCell ref="G89:L89"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="G91:L91"/>
+    <mergeCell ref="G92:L92"/>
+    <mergeCell ref="G72:L72"/>
+    <mergeCell ref="G73:L73"/>
+    <mergeCell ref="G74:L74"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="G76:L76"/>
+    <mergeCell ref="G77:L77"/>
+    <mergeCell ref="G78:L78"/>
+    <mergeCell ref="G79:L79"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="G81:L81"/>
     <mergeCell ref="N6:P6"/>
     <mergeCell ref="R6:W6"/>
     <mergeCell ref="R7:W7"/>
@@ -1842,83 +1924,6 @@
     <mergeCell ref="G53:L53"/>
     <mergeCell ref="G54:L54"/>
     <mergeCell ref="C56:E56"/>
-    <mergeCell ref="G87:L87"/>
-    <mergeCell ref="G93:L93"/>
-    <mergeCell ref="G94:L94"/>
-    <mergeCell ref="G88:L88"/>
-    <mergeCell ref="G89:L89"/>
-    <mergeCell ref="C91:E91"/>
-    <mergeCell ref="G91:L91"/>
-    <mergeCell ref="G92:L92"/>
-    <mergeCell ref="G72:L72"/>
-    <mergeCell ref="G73:L73"/>
-    <mergeCell ref="G74:L74"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="G76:L76"/>
-    <mergeCell ref="G77:L77"/>
-    <mergeCell ref="G78:L78"/>
-    <mergeCell ref="G79:L79"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="G81:L81"/>
-    <mergeCell ref="G56:L56"/>
-    <mergeCell ref="G57:L57"/>
-    <mergeCell ref="G58:L58"/>
-    <mergeCell ref="G59:L59"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="G61:L61"/>
-    <mergeCell ref="G42:L42"/>
-    <mergeCell ref="G43:L43"/>
-    <mergeCell ref="G44:L44"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="G46:L46"/>
-    <mergeCell ref="G47:L47"/>
-    <mergeCell ref="G48:L48"/>
-    <mergeCell ref="G49:L49"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="G51:L51"/>
-    <mergeCell ref="G32:L32"/>
-    <mergeCell ref="G33:L33"/>
-    <mergeCell ref="G34:L34"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="G36:L36"/>
-    <mergeCell ref="G37:L37"/>
-    <mergeCell ref="G38:L38"/>
-    <mergeCell ref="G39:L39"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="G41:L41"/>
-    <mergeCell ref="G23:L23"/>
-    <mergeCell ref="G24:L24"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="G26:L26"/>
-    <mergeCell ref="G27:L27"/>
-    <mergeCell ref="G28:L28"/>
-    <mergeCell ref="G29:L29"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="G31:L31"/>
-    <mergeCell ref="G2:Q3"/>
-    <mergeCell ref="G99:L99"/>
-    <mergeCell ref="C96:E96"/>
-    <mergeCell ref="G96:L96"/>
-    <mergeCell ref="G97:L97"/>
-    <mergeCell ref="G98:L98"/>
-    <mergeCell ref="G9:L9"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="G12:L12"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="G6:L6"/>
-    <mergeCell ref="G7:L7"/>
-    <mergeCell ref="G8:L8"/>
-    <mergeCell ref="G13:L13"/>
-    <mergeCell ref="G14:L14"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="G16:L16"/>
-    <mergeCell ref="G17:L17"/>
-    <mergeCell ref="G18:L18"/>
-    <mergeCell ref="G19:L19"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="G21:L21"/>
-    <mergeCell ref="G22:L22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
